--- a/output/wisconsin_wages_2025.xlsx
+++ b/output/wisconsin_wages_2025.xlsx
@@ -402,14 +402,14 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Black Women</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Black Men</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Black Women</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>Hispanic</t>
@@ -417,12 +417,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Hispanic Women</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Hispanic Men</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Hispanic Women</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -441,37 +441,37 @@
         <v>1979</v>
       </c>
       <c r="B2">
-        <v>21.2132745444097</v>
+        <v>19.7900417786966</v>
       </c>
       <c r="C2">
-        <v>28.0008751221738</v>
+        <v>26.1222512982521</v>
       </c>
       <c r="D2">
-        <v>16.2461724306342</v>
+        <v>15.1561905481908</v>
       </c>
       <c r="E2">
-        <v>21.3588951516339</v>
+        <v>19.925892464774</v>
       </c>
       <c r="F2">
-        <v>24.3397201306968</v>
+        <v>17.0164572407776</v>
       </c>
       <c r="G2">
-        <v>18.2402232020754</v>
+        <v>22.7067290936094</v>
       </c>
       <c r="H2">
-        <v>21.2245554748795</v>
+        <v>19.8005658533666</v>
       </c>
       <c r="I2">
-        <v>22.2954943132108</v>
+        <v>12.457142677142</v>
       </c>
       <c r="J2">
-        <v>13.3530181797575</v>
+        <v>20.7996536796537</v>
       </c>
       <c r="K2">
-        <v>16.3046116591126</v>
+        <v>15.2107089946796</v>
       </c>
       <c r="L2">
-        <v>27.8151832749107</v>
+        <v>25.9490178161885</v>
       </c>
     </row>
     <row r="3">
@@ -479,37 +479,37 @@
         <v>1980</v>
       </c>
       <c r="B3">
-        <v>21.0015999586164</v>
+        <v>19.6207367395472</v>
       </c>
       <c r="C3">
-        <v>27.0246998162649</v>
+        <v>25.2478154809666</v>
       </c>
       <c r="D3">
-        <v>15.8266968055563</v>
+        <v>14.7860854454115</v>
       </c>
       <c r="E3">
-        <v>18.3282453482963</v>
+        <v>17.1231562159726</v>
       </c>
       <c r="F3">
-        <v>24.7690397899607</v>
+        <v>15.2084956678127</v>
       </c>
       <c r="G3">
-        <v>16.2788353071355</v>
+        <v>23.1404659629658</v>
       </c>
       <c r="H3">
-        <v>20.6731317007664</v>
+        <v>19.3138653951128</v>
       </c>
       <c r="I3">
-        <v>28.1226200592227</v>
+        <v>14.8970911899738</v>
       </c>
       <c r="J3">
-        <v>15.9455148841714</v>
+        <v>26.2735470485873</v>
       </c>
       <c r="K3">
-        <v>15.850095957119</v>
+        <v>14.8079460938214</v>
       </c>
       <c r="L3">
-        <v>27.0177570766206</v>
+        <v>25.2413292291058</v>
       </c>
     </row>
     <row r="4">
@@ -517,37 +517,37 @@
         <v>1981</v>
       </c>
       <c r="B4">
-        <v>20.4816678648454</v>
+        <v>19.1157295373665</v>
       </c>
       <c r="C4">
-        <v>26.501593449234</v>
+        <v>24.7341816119537</v>
       </c>
       <c r="D4">
-        <v>15.6962887714614</v>
+        <v>14.6494910900618</v>
       </c>
       <c r="E4">
-        <v>22.1547806597202</v>
+        <v>20.6772611413053</v>
       </c>
       <c r="F4">
-        <v>24.7349390856745</v>
+        <v>14.0314419289586</v>
       </c>
       <c r="G4">
-        <v>15.0340761356779</v>
+        <v>23.0853467991513</v>
       </c>
       <c r="H4">
-        <v>19.7701293525723</v>
+        <v>18.4516440807628</v>
       </c>
       <c r="I4">
-        <v>23.0352263035833</v>
+        <v>14.4298935343786</v>
       </c>
       <c r="J4">
-        <v>15.4609995981843</v>
+        <v>21.4989891817901</v>
       </c>
       <c r="K4">
-        <v>15.6942200660706</v>
+        <v>14.6475603482392</v>
       </c>
       <c r="L4">
-        <v>26.4450378215716</v>
+        <v>24.6813977229977</v>
       </c>
     </row>
     <row r="5">
@@ -555,37 +555,37 @@
         <v>1982</v>
       </c>
       <c r="B5">
-        <v>20.5642543728069</v>
+        <v>19.190817322187</v>
       </c>
       <c r="C5">
-        <v>26.0093461941865</v>
+        <v>24.2722445673591</v>
       </c>
       <c r="D5">
-        <v>16.0159831321846</v>
+        <v>14.9463141698645</v>
       </c>
       <c r="E5">
-        <v>21.8488134755927</v>
+        <v>20.3895838144802</v>
       </c>
       <c r="F5">
-        <v>26.2981305332507</v>
+        <v>14.8485798813993</v>
       </c>
       <c r="G5">
-        <v>15.911254254034</v>
+        <v>24.5417416955321</v>
       </c>
       <c r="H5">
-        <v>15.9675476041891</v>
+        <v>14.9011135341977</v>
       </c>
       <c r="I5">
-        <v>20.0803389112828</v>
+        <v>11.634469781914</v>
       </c>
       <c r="J5">
-        <v>12.4671186261258</v>
+        <v>18.7392214095353</v>
       </c>
       <c r="K5">
-        <v>15.9766715938762</v>
+        <v>14.9096281545754</v>
       </c>
       <c r="L5">
-        <v>25.8385425810087</v>
+        <v>24.1128485163746</v>
       </c>
     </row>
     <row r="6">
@@ -593,37 +593,37 @@
         <v>1983</v>
       </c>
       <c r="B6">
-        <v>20.030640453604</v>
+        <v>18.7065765002461</v>
       </c>
       <c r="C6">
-        <v>25.9767681259483</v>
+        <v>24.2596536692252</v>
       </c>
       <c r="D6">
-        <v>15.8924876418938</v>
+        <v>14.8419635678105</v>
       </c>
       <c r="E6">
-        <v>22.3479519956909</v>
+        <v>20.8707092815897</v>
       </c>
       <c r="F6">
-        <v>26.9307186141591</v>
+        <v>14.3833662864206</v>
       </c>
       <c r="G6">
-        <v>15.4014305392539</v>
+        <v>25.1505461909345</v>
       </c>
       <c r="H6">
-        <v>15.0357607282185</v>
+        <v>14.0418679549114</v>
       </c>
       <c r="I6">
-        <v>16.1183353285796</v>
+        <v>14.0418679549114</v>
       </c>
       <c r="J6">
-        <v>15.0357607282185</v>
+        <v>15.0528822869686</v>
       </c>
       <c r="K6">
-        <v>15.8857772316207</v>
+        <v>14.8356967285943</v>
       </c>
       <c r="L6">
-        <v>25.9687634004263</v>
+        <v>24.2521780714935</v>
       </c>
     </row>
     <row r="7">
@@ -631,37 +631,37 @@
         <v>1984</v>
       </c>
       <c r="B7">
-        <v>19.8938513233718</v>
+        <v>18.5742737745612</v>
       </c>
       <c r="C7">
-        <v>25.222595747044</v>
+        <v>23.5495576545444</v>
       </c>
       <c r="D7">
-        <v>15.9617353616731</v>
+        <v>14.9029786995795</v>
       </c>
       <c r="E7">
-        <v>16.0864542887898</v>
+        <v>15.0194249049663</v>
       </c>
       <c r="F7">
-        <v>21.7103620474407</v>
+        <v>13.4775888717156</v>
       </c>
       <c r="G7">
-        <v>14.4350811485643</v>
+        <v>20.2702936630603</v>
       </c>
       <c r="H7">
-        <v>19.5889144741492</v>
+        <v>18.2895636684412</v>
       </c>
       <c r="I7">
-        <v>28.2188519467129</v>
+        <v>11.1324883309177</v>
       </c>
       <c r="J7">
-        <v>11.9233769461159</v>
+        <v>26.3470694106513</v>
       </c>
       <c r="K7">
-        <v>15.8517605430922</v>
+        <v>14.8002986123794</v>
       </c>
       <c r="L7">
-        <v>25.1228149225947</v>
+        <v>23.4563953844215</v>
       </c>
     </row>
     <row r="8">
@@ -669,37 +669,37 @@
         <v>1985</v>
       </c>
       <c r="B8">
-        <v>19.7679648479978</v>
+        <v>18.451467743148</v>
       </c>
       <c r="C8">
-        <v>25.2800159725014</v>
+        <v>23.5964300245162</v>
       </c>
       <c r="D8">
-        <v>16.2266002948157</v>
+        <v>15.1459492275996</v>
       </c>
       <c r="E8">
-        <v>17.4247434533737</v>
+        <v>16.2642990431622</v>
       </c>
       <c r="F8">
-        <v>20.7789855072464</v>
+        <v>15.1125811977415</v>
       </c>
       <c r="G8">
-        <v>16.1908514833681</v>
+        <v>19.3951569506726</v>
       </c>
       <c r="H8">
-        <v>15.0256643044776</v>
+        <v>14.0249925758807</v>
       </c>
       <c r="I8">
-        <v>14.5184787978297</v>
+        <v>14.598504983078</v>
       </c>
       <c r="J8">
-        <v>15.6400963520082</v>
+        <v>13.5515843577021</v>
       </c>
       <c r="K8">
-        <v>16.1148851058909</v>
+        <v>15.0416739913416</v>
       </c>
       <c r="L8">
-        <v>25.0152172932878</v>
+        <v>23.3492662762241</v>
       </c>
     </row>
     <row r="9">
@@ -707,37 +707,37 @@
         <v>1986</v>
       </c>
       <c r="B9">
-        <v>20.508194965025</v>
+        <v>19.151171942767</v>
       </c>
       <c r="C9">
-        <v>26.6953682757896</v>
+        <v>24.9289412743064</v>
       </c>
       <c r="D9">
-        <v>16.0941211925266</v>
+        <v>15.0291765195061</v>
       </c>
       <c r="E9">
-        <v>17.7196071252687</v>
+        <v>16.5471043840296</v>
       </c>
       <c r="F9">
-        <v>18.8493466801994</v>
+        <v>15.2548703240787</v>
       </c>
       <c r="G9">
-        <v>16.3358073180758</v>
+        <v>17.6020893061021</v>
       </c>
       <c r="H9">
-        <v>16.8576306727606</v>
+        <v>15.7421647352331</v>
       </c>
       <c r="I9">
-        <v>19.6370252025382</v>
+        <v>12.8235294117647</v>
       </c>
       <c r="J9">
-        <v>13.7321852731591</v>
+        <v>18.3376473034129</v>
       </c>
       <c r="K9">
-        <v>16.0336996611394</v>
+        <v>14.972753068363</v>
       </c>
       <c r="L9">
-        <v>26.385326099509</v>
+        <v>24.6394145247516</v>
       </c>
     </row>
     <row r="10">
@@ -745,37 +745,37 @@
         <v>1987</v>
       </c>
       <c r="B10">
-        <v>19.7586587843438</v>
+        <v>18.451668817512</v>
       </c>
       <c r="C10">
-        <v>24.9786010355459</v>
+        <v>23.3263238594847</v>
       </c>
       <c r="D10">
-        <v>16.0773080289535</v>
+        <v>15.0138309722944</v>
       </c>
       <c r="E10">
-        <v>18.1036473676297</v>
+        <v>16.9061326106412</v>
       </c>
       <c r="F10">
-        <v>18.2502871912694</v>
+        <v>16.6302681987214</v>
       </c>
       <c r="G10">
-        <v>17.8082426083218</v>
+        <v>17.0430725462304</v>
       </c>
       <c r="H10">
-        <v>18.5212523768785</v>
+        <v>17.2961140062053</v>
       </c>
       <c r="I10">
-        <v>23.9086731763354</v>
+        <v>13.4856101566494</v>
       </c>
       <c r="J10">
-        <v>14.4408385073023</v>
+        <v>22.3271692745377</v>
       </c>
       <c r="K10">
-        <v>16.0878803865585</v>
+        <v>15.023703992689</v>
       </c>
       <c r="L10">
-        <v>24.6363234725374</v>
+        <v>23.0066871723376</v>
       </c>
     </row>
     <row r="11">
@@ -783,37 +783,37 @@
         <v>1988</v>
       </c>
       <c r="B11">
-        <v>19.8677702082161</v>
+        <v>18.5495573184585</v>
       </c>
       <c r="C11">
-        <v>24.9725512137373</v>
+        <v>23.3156396149477</v>
       </c>
       <c r="D11">
-        <v>16.0162511770085</v>
+        <v>14.9535839261865</v>
       </c>
       <c r="E11">
-        <v>16.5628808277796</v>
+        <v>15.4639450755597</v>
       </c>
       <c r="F11">
-        <v>16.6520498399919</v>
+        <v>15.0199309134778</v>
       </c>
       <c r="G11">
-        <v>16.0873130721729</v>
+        <v>15.5471977851355</v>
       </c>
       <c r="H11">
-        <v>16.6643491438551</v>
+        <v>15.5586810386459</v>
       </c>
       <c r="I11">
-        <v>19.3711911357341</v>
+        <v>14.0046307640965</v>
       </c>
       <c r="J11">
-        <v>14.9998612417078</v>
+        <v>18.0859259259259</v>
       </c>
       <c r="K11">
-        <v>15.9791827981162</v>
+        <v>14.9189750087408</v>
       </c>
       <c r="L11">
-        <v>24.5191906852405</v>
+        <v>22.8923592457294</v>
       </c>
     </row>
     <row r="12">
@@ -821,37 +821,37 @@
         <v>1989</v>
       </c>
       <c r="B12">
-        <v>19.8917302981502</v>
+        <v>18.5597861976974</v>
       </c>
       <c r="C12">
-        <v>24.7191912863271</v>
+        <v>23.0640018931325</v>
       </c>
       <c r="D12">
-        <v>16.3467426332969</v>
+        <v>15.2521698090281</v>
       </c>
       <c r="E12">
-        <v>16.1635994657961</v>
+        <v>15.0812898513052</v>
       </c>
       <c r="F12">
-        <v>20.1702066665625</v>
+        <v>13.0417283816845</v>
       </c>
       <c r="G12">
-        <v>13.9776687525842</v>
+        <v>18.8196158747228</v>
       </c>
       <c r="H12">
-        <v>14.775438023829</v>
+        <v>13.7860792695896</v>
       </c>
       <c r="I12">
-        <v>12.9509823510954</v>
+        <v>16.0558004901099</v>
       </c>
       <c r="J12">
-        <v>17.2080459154102</v>
+        <v>12.0837885836828</v>
       </c>
       <c r="K12">
-        <v>16.2320271769041</v>
+        <v>15.1451356640689</v>
       </c>
       <c r="L12">
-        <v>24.5384534849996</v>
+        <v>22.8953662390088</v>
       </c>
     </row>
     <row r="13">
@@ -859,37 +859,37 @@
         <v>1990</v>
       </c>
       <c r="B13">
-        <v>19.7582995915702</v>
+        <v>18.4488100217279</v>
       </c>
       <c r="C13">
-        <v>24.1706040296477</v>
+        <v>22.5686871376133</v>
       </c>
       <c r="D13">
-        <v>16.2686402824244</v>
+        <v>15.1904293429344</v>
       </c>
       <c r="E13">
-        <v>17.1110286705407</v>
+        <v>15.9769880882779</v>
       </c>
       <c r="F13">
-        <v>18.2116394064687</v>
+        <v>15.0078911385978</v>
       </c>
       <c r="G13">
-        <v>16.0731455852628</v>
+        <v>17.0046553873239</v>
       </c>
       <c r="H13">
-        <v>21.5802122827484</v>
+        <v>20.1499746872369</v>
       </c>
       <c r="I13">
-        <v>21.6504301619433</v>
+        <v>15.2982456140351</v>
       </c>
       <c r="J13">
-        <v>16.3841093117409</v>
+        <v>20.2155388471178</v>
       </c>
       <c r="K13">
-        <v>16.2339104524991</v>
+        <v>15.158001247014</v>
       </c>
       <c r="L13">
-        <v>23.7875137951693</v>
+        <v>22.2109863686621</v>
       </c>
     </row>
     <row r="14">
@@ -897,37 +897,37 @@
         <v>1991</v>
       </c>
       <c r="B14">
-        <v>19.7742838622071</v>
+        <v>18.4654523251221</v>
       </c>
       <c r="C14">
-        <v>23.4355960437097</v>
+        <v>21.8844274954006</v>
       </c>
       <c r="D14">
-        <v>16.6418701619841</v>
+        <v>15.5403686028957</v>
       </c>
       <c r="E14">
-        <v>17.6463622529991</v>
+        <v>16.478374800584</v>
       </c>
       <c r="F14">
-        <v>20.6499025505036</v>
+        <v>15.5310897926783</v>
       </c>
       <c r="G14">
-        <v>16.6319336695597</v>
+        <v>19.283115066104</v>
       </c>
       <c r="H14">
-        <v>21.047363022808</v>
+        <v>19.654268198809</v>
       </c>
       <c r="I14">
-        <v>21.453857421875</v>
+        <v>19.4324194188331</v>
       </c>
       <c r="J14">
-        <v>20.8097895979881</v>
+        <v>20.0338573155985</v>
       </c>
       <c r="K14">
-        <v>16.608447234612</v>
+        <v>15.5091578912331</v>
       </c>
       <c r="L14">
-        <v>23.2437913212925</v>
+        <v>21.7053180529446</v>
       </c>
     </row>
     <row r="15">
@@ -935,37 +935,37 @@
         <v>1992</v>
       </c>
       <c r="B15">
-        <v>19.9648402724282</v>
+        <v>18.6344753524492</v>
       </c>
       <c r="C15">
-        <v>23.4738765891931</v>
+        <v>21.9096856653465</v>
       </c>
       <c r="D15">
-        <v>16.5162518638949</v>
+        <v>15.4156849778373</v>
       </c>
       <c r="E15">
-        <v>15.9308002970797</v>
+        <v>14.8692452045657</v>
       </c>
       <c r="F15">
-        <v>17.5216770899074</v>
+        <v>14.0054716981132</v>
       </c>
       <c r="G15">
-        <v>15.0053596950929</v>
+        <v>16.354113301691</v>
       </c>
       <c r="H15">
-        <v>16.2084325112974</v>
+        <v>15.1283772878827</v>
       </c>
       <c r="I15">
-        <v>21.8139590281086</v>
+        <v>13.9437736241323</v>
       </c>
       <c r="J15">
-        <v>14.9392568309742</v>
+        <v>20.3603773584906</v>
       </c>
       <c r="K15">
-        <v>16.4561782489793</v>
+        <v>15.3596143916868</v>
       </c>
       <c r="L15">
-        <v>23.0566937813252</v>
+        <v>21.5203019966269</v>
       </c>
     </row>
     <row r="16">
@@ -973,37 +973,37 @@
         <v>1993</v>
       </c>
       <c r="B16">
-        <v>20.5133364213887</v>
+        <v>19.1555019470847</v>
       </c>
       <c r="C16">
-        <v>23.8729089055363</v>
+        <v>22.2926950364722</v>
       </c>
       <c r="D16">
-        <v>17.4935465630102</v>
+        <v>16.3356003316829</v>
       </c>
       <c r="E16">
-        <v>14.1844795539033</v>
+        <v>13.2455696202532</v>
       </c>
       <c r="F16">
-        <v>14.9710734692648</v>
+        <v>12.7679263674403</v>
       </c>
       <c r="G16">
-        <v>13.6729786409321</v>
+        <v>13.9800967087652</v>
       </c>
       <c r="H16">
-        <v>16.7368728210492</v>
+        <v>15.6290129175395</v>
       </c>
       <c r="I16">
-        <v>17.476997419804</v>
+        <v>12.3167743243008</v>
       </c>
       <c r="J16">
-        <v>13.1898467624941</v>
+        <v>16.3201466220377</v>
       </c>
       <c r="K16">
-        <v>17.2902691175947</v>
+        <v>16.1457783826119</v>
       </c>
       <c r="L16">
-        <v>23.5155746351831</v>
+        <v>21.9590137098025</v>
       </c>
     </row>
     <row r="17">
@@ -1011,37 +1011,37 @@
         <v>1994</v>
       </c>
       <c r="B17">
-        <v>20.5318001415928</v>
+        <v>19.1548547370155</v>
       </c>
       <c r="C17">
-        <v>23.8523223631264</v>
+        <v>22.2526893333916</v>
       </c>
       <c r="D17">
-        <v>17.0813017549111</v>
+        <v>15.9357607018411</v>
       </c>
       <c r="E17">
-        <v>14.7581498309271</v>
+        <v>13.768408724467</v>
       </c>
       <c r="F17">
-        <v>16.3064406490022</v>
+        <v>13.0744224843893</v>
       </c>
       <c r="G17">
-        <v>14.0142764381023</v>
+        <v>15.2128649098164</v>
       </c>
       <c r="H17">
-        <v>17.2892503527874</v>
+        <v>16.1297634272532</v>
       </c>
       <c r="I17">
-        <v>17.1802259630977</v>
+        <v>16.3403003881644</v>
       </c>
       <c r="J17">
-        <v>17.5149217485351</v>
+        <v>16.0280506532686</v>
       </c>
       <c r="K17">
-        <v>16.8839476148703</v>
+        <v>15.7516419271521</v>
       </c>
       <c r="L17">
-        <v>23.3969508380743</v>
+        <v>21.8278568611489</v>
       </c>
     </row>
     <row r="18">
@@ -1049,37 +1049,37 @@
         <v>1995</v>
       </c>
       <c r="B18">
-        <v>20.5615576171875</v>
+        <v>19.191520730198</v>
       </c>
       <c r="C18">
-        <v>24.3658265007867</v>
+        <v>22.7423074216601</v>
       </c>
       <c r="D18">
-        <v>17.2258010673523</v>
+        <v>16.0780289330813</v>
       </c>
       <c r="E18">
-        <v>16.4189555602603</v>
+        <v>15.3249443388248</v>
       </c>
       <c r="F18">
-        <v>17.575</v>
+        <v>15.0448298834705</v>
       </c>
       <c r="G18">
-        <v>16.1188444021013</v>
+        <v>16.4039603960396</v>
       </c>
       <c r="H18">
-        <v>17.8882667795817</v>
+        <v>16.6963539007709</v>
       </c>
       <c r="I18">
-        <v>19.5277777777778</v>
+        <v>15.1277127531784</v>
       </c>
       <c r="J18">
-        <v>16.2076440821754</v>
+        <v>18.2266226622662</v>
       </c>
       <c r="K18">
-        <v>17.0372665521834</v>
+        <v>15.9020566588214</v>
       </c>
       <c r="L18">
-        <v>23.9085775989956</v>
+        <v>22.3155254656936</v>
       </c>
     </row>
     <row r="19">
@@ -1087,37 +1087,37 @@
         <v>1996</v>
       </c>
       <c r="B19">
-        <v>20.9849664184438</v>
+        <v>19.5917557688363</v>
       </c>
       <c r="C19">
-        <v>25.343238091572</v>
+        <v>23.6606778958271</v>
       </c>
       <c r="D19">
-        <v>17.9956545602708</v>
+        <v>16.8009069928888</v>
       </c>
       <c r="E19">
-        <v>15.2692274190647</v>
+        <v>14.2554897829242</v>
       </c>
       <c r="F19">
-        <v>15.1003246524117</v>
+        <v>14.2934728545979</v>
       </c>
       <c r="G19">
-        <v>15.309911546253</v>
+        <v>14.0978006216951</v>
       </c>
       <c r="H19">
-        <v>16.6649494501419</v>
+        <v>15.558548582676</v>
       </c>
       <c r="I19">
-        <v>16.7639894733181</v>
+        <v>15.0884974060386</v>
       </c>
       <c r="J19">
-        <v>16.1614719531237</v>
+        <v>15.6510132503203</v>
       </c>
       <c r="K19">
-        <v>17.7328708512442</v>
+        <v>16.555569728839</v>
       </c>
       <c r="L19">
-        <v>24.8296471983839</v>
+        <v>23.1811847604177</v>
       </c>
     </row>
     <row r="20">
@@ -1125,37 +1125,37 @@
         <v>1997</v>
       </c>
       <c r="B20">
-        <v>21.685671234535</v>
+        <v>20.2500786918008</v>
       </c>
       <c r="C20">
-        <v>25.876137996124</v>
+        <v>24.1631363398581</v>
       </c>
       <c r="D20">
-        <v>18.569640111115</v>
+        <v>17.3403289878181</v>
       </c>
       <c r="E20">
-        <v>15.7574339478703</v>
+        <v>14.7142910161374</v>
       </c>
       <c r="F20">
-        <v>17.2642823033414</v>
+        <v>13.6379701951818</v>
       </c>
       <c r="G20">
-        <v>14.6048093175484</v>
+        <v>16.1213859335548</v>
       </c>
       <c r="H20">
-        <v>17.7004236690069</v>
+        <v>16.5286547185492</v>
       </c>
       <c r="I20">
-        <v>19.5974576271186</v>
+        <v>14.5668835257083</v>
       </c>
       <c r="J20">
-        <v>15.5995762711864</v>
+        <v>18.3001049317943</v>
       </c>
       <c r="K20">
-        <v>18.1837165577937</v>
+        <v>16.9799535934272</v>
       </c>
       <c r="L20">
-        <v>25.2197568335776</v>
+        <v>23.5502076437791</v>
       </c>
     </row>
     <row r="21">
@@ -1163,37 +1163,37 @@
         <v>1998</v>
       </c>
       <c r="B21">
-        <v>21.9453497654618</v>
+        <v>20.4909125305555</v>
       </c>
       <c r="C21">
-        <v>25.7417087431337</v>
+        <v>24.0356662290585</v>
       </c>
       <c r="D21">
-        <v>19.0120562043876</v>
+        <v>17.752024227166</v>
       </c>
       <c r="E21">
-        <v>18.3231463480155</v>
+        <v>17.1087721596791</v>
       </c>
       <c r="F21">
-        <v>19.5518398484258</v>
+        <v>15.5018132957316</v>
       </c>
       <c r="G21">
-        <v>16.6021261506256</v>
+        <v>18.2560334844174</v>
       </c>
       <c r="H21">
-        <v>15.8504644295444</v>
+        <v>14.7999682696167</v>
       </c>
       <c r="I21">
-        <v>15.4900501693372</v>
+        <v>15.1652173913043</v>
       </c>
       <c r="J21">
-        <v>16.2416387959866</v>
+        <v>14.4634406152571</v>
       </c>
       <c r="K21">
-        <v>18.870464102879</v>
+        <v>17.6198162014094</v>
       </c>
       <c r="L21">
-        <v>25.0490751274453</v>
+        <v>23.3889371959615</v>
       </c>
     </row>
     <row r="22">
@@ -1201,37 +1201,37 @@
         <v>1999</v>
       </c>
       <c r="B22">
-        <v>21.9848487593911</v>
+        <v>20.5317974166406</v>
       </c>
       <c r="C22">
-        <v>24.8859470540827</v>
+        <v>23.2411525331695</v>
       </c>
       <c r="D22">
-        <v>19.0765151833043</v>
+        <v>17.8156852223859</v>
       </c>
       <c r="E22">
-        <v>18.2977271080017</v>
+        <v>17.0883698258777</v>
       </c>
       <c r="F22">
-        <v>19.4271645401463</v>
+        <v>16.7261270352068</v>
       </c>
       <c r="G22">
-        <v>17.9098481120485</v>
+        <v>18.1431590038864</v>
       </c>
       <c r="H22">
-        <v>18.3560606927583</v>
+        <v>17.1428479511501</v>
       </c>
       <c r="I22">
-        <v>18.7916661753799</v>
+        <v>15.4943610547667</v>
       </c>
       <c r="J22">
-        <v>16.5909090909091</v>
+        <v>17.5496628271881</v>
       </c>
       <c r="K22">
-        <v>18.9030304822055</v>
+        <v>17.6536666987731</v>
       </c>
       <c r="L22">
-        <v>24.4999998988527</v>
+        <v>22.8807139014811</v>
       </c>
     </row>
     <row r="23">
@@ -1239,37 +1239,37 @@
         <v>2000</v>
       </c>
       <c r="B23">
-        <v>22.2712614078333</v>
+        <v>20.7893432401769</v>
       </c>
       <c r="C23">
-        <v>25.5234058455666</v>
+        <v>23.8250916760015</v>
       </c>
       <c r="D23">
-        <v>19.3103365945344</v>
+        <v>18.0254368262197</v>
       </c>
       <c r="E23">
-        <v>18.385703009426</v>
+        <v>17.1623278796626</v>
       </c>
       <c r="F23">
-        <v>18.2472279463664</v>
+        <v>17.1835294117647</v>
       </c>
       <c r="G23">
-        <v>18.4084158415842</v>
+        <v>17.033066875383</v>
       </c>
       <c r="H23">
-        <v>16.2873268165211</v>
+        <v>15.2035765488568</v>
       </c>
       <c r="I23">
-        <v>16.4851485148515</v>
+        <v>14.4047563314999</v>
       </c>
       <c r="J23">
-        <v>15.4315646275435</v>
+        <v>15.3882352941176</v>
       </c>
       <c r="K23">
-        <v>19.087603924062</v>
+        <v>17.8175246719659</v>
       </c>
       <c r="L23">
-        <v>24.4525474246185</v>
+        <v>22.8254876182406</v>
       </c>
     </row>
     <row r="24">
@@ -1277,37 +1277,37 @@
         <v>2001</v>
       </c>
       <c r="B24">
-        <v>23.0877437709063</v>
+        <v>21.6772346462934</v>
       </c>
       <c r="C24">
-        <v>27.0375847733842</v>
+        <v>25.3857663709982</v>
       </c>
       <c r="D24">
-        <v>19.6734372331034</v>
+        <v>18.4715197566646</v>
       </c>
       <c r="E24">
-        <v>16.9563150956716</v>
+        <v>15.9203958911109</v>
       </c>
       <c r="F24">
-        <v>17.8493776181867</v>
+        <v>15.4415066074799</v>
       </c>
       <c r="G24">
-        <v>16.4462651167184</v>
+        <v>16.7588981738141</v>
       </c>
       <c r="H24">
-        <v>15.7146706652724</v>
+        <v>14.7546077598799</v>
       </c>
       <c r="I24">
-        <v>16.0209857256173</v>
+        <v>13.5640728794877</v>
       </c>
       <c r="J24">
-        <v>14.4466692473184</v>
+        <v>15.0422089869498</v>
       </c>
       <c r="K24">
-        <v>19.3156526489904</v>
+        <v>18.1355934548309</v>
       </c>
       <c r="L24">
-        <v>25.7724714499508</v>
+        <v>24.1979431415679</v>
       </c>
     </row>
     <row r="25">
@@ -1315,37 +1315,37 @@
         <v>2002</v>
       </c>
       <c r="B25">
-        <v>23.4122945776123</v>
+        <v>22.0541130464727</v>
       </c>
       <c r="C25">
-        <v>26.917930874886</v>
+        <v>25.3563822428385</v>
       </c>
       <c r="D25">
-        <v>20.5269351161005</v>
+        <v>19.3361375172933</v>
       </c>
       <c r="E25">
-        <v>19.0021227561135</v>
+        <v>17.8997817577015</v>
       </c>
       <c r="F25">
-        <v>20.372038023141</v>
+        <v>16.7146543866938</v>
       </c>
       <c r="G25">
-        <v>17.7440104455637</v>
+        <v>19.1902262317773</v>
       </c>
       <c r="H25">
-        <v>16.9406842679305</v>
+        <v>15.9579303383105</v>
       </c>
       <c r="I25">
-        <v>17.774166088379</v>
+        <v>14.5630610344627</v>
       </c>
       <c r="J25">
-        <v>15.4599132675217</v>
+        <v>16.7430606564608</v>
       </c>
       <c r="K25">
-        <v>20.0935807166631</v>
+        <v>18.9279226418698</v>
       </c>
       <c r="L25">
-        <v>26.0792582210399</v>
+        <v>24.5663622191458</v>
       </c>
     </row>
     <row r="26">
@@ -1353,37 +1353,37 @@
         <v>2003</v>
       </c>
       <c r="B26">
-        <v>23.4849888806523</v>
+        <v>22.1640074211503</v>
       </c>
       <c r="C26">
-        <v>26.5226486543976</v>
+        <v>25.030805191861</v>
       </c>
       <c r="D26">
-        <v>20.8985544011008</v>
+        <v>19.7230544664599</v>
       </c>
       <c r="E26">
-        <v>18.4903898885994</v>
+        <v>17.4503441663753</v>
       </c>
       <c r="F26">
-        <v>18.5411416909887</v>
+        <v>17.4215420939883</v>
       </c>
       <c r="G26">
-        <v>18.4598712040991</v>
+        <v>17.4982412861274</v>
       </c>
       <c r="H26">
-        <v>16.7722492504332</v>
+        <v>15.8288453422362</v>
       </c>
       <c r="I26">
-        <v>17.1594699777613</v>
+        <v>14.6211782819928</v>
       </c>
       <c r="J26">
-        <v>15.4926048728428</v>
+        <v>16.1942857142857</v>
       </c>
       <c r="K26">
-        <v>20.5632507102944</v>
+        <v>19.4066109063143</v>
       </c>
       <c r="L26">
-        <v>25.7205773071504</v>
+        <v>24.273848678787</v>
       </c>
     </row>
     <row r="27">
@@ -1391,37 +1391,37 @@
         <v>2004</v>
       </c>
       <c r="B27">
-        <v>23.1597292724499</v>
+        <v>21.8920137845553</v>
       </c>
       <c r="C27">
-        <v>26.2759145468151</v>
+        <v>24.8376255479355</v>
       </c>
       <c r="D27">
-        <v>20.2757496231299</v>
+        <v>19.1658971924933</v>
       </c>
       <c r="E27">
-        <v>18.3455311055648</v>
+        <v>17.3413348283724</v>
       </c>
       <c r="F27">
-        <v>17.6284293353772</v>
+        <v>17.6881056002103</v>
       </c>
       <c r="G27">
-        <v>18.7123825644758</v>
+        <v>16.6634857199828</v>
       </c>
       <c r="H27">
-        <v>16.6987545584944</v>
+        <v>15.7846994098646</v>
       </c>
       <c r="I27">
-        <v>17.3158662654863</v>
+        <v>13.9405573095261</v>
       </c>
       <c r="J27">
-        <v>14.7478224878277</v>
+        <v>16.3680317034829</v>
       </c>
       <c r="K27">
-        <v>19.8945125793292</v>
+        <v>18.80552827281</v>
       </c>
       <c r="L27">
-        <v>25.3659267184536</v>
+        <v>23.9774485636577</v>
       </c>
     </row>
     <row r="28">
@@ -1429,37 +1429,37 @@
         <v>2005</v>
       </c>
       <c r="B28">
-        <v>23.4095410195143</v>
+        <v>22.2351565355823</v>
       </c>
       <c r="C28">
-        <v>27.1713496286776</v>
+        <v>25.8082468072762</v>
       </c>
       <c r="D28">
-        <v>20.2603420215612</v>
+        <v>19.243943140035</v>
       </c>
       <c r="E28">
-        <v>18.7848638539208</v>
+        <v>17.842485162069</v>
       </c>
       <c r="F28">
-        <v>21.1206179724059</v>
+        <v>16.4178350137595</v>
       </c>
       <c r="G28">
-        <v>17.2849685852754</v>
+        <v>20.0610616992961</v>
       </c>
       <c r="H28">
-        <v>16.2856255813018</v>
+        <v>15.4686259665779</v>
       </c>
       <c r="I28">
-        <v>19.0529330249605</v>
+        <v>13.3507267306285</v>
       </c>
       <c r="J28">
-        <v>14.055866192839</v>
+        <v>18.0971061294542</v>
       </c>
       <c r="K28">
-        <v>19.7189072756794</v>
+        <v>18.7296705057082</v>
       </c>
       <c r="L28">
-        <v>26.4800324519919</v>
+        <v>25.1516108815001</v>
       </c>
     </row>
     <row r="29">
@@ -1467,37 +1467,37 @@
         <v>2006</v>
       </c>
       <c r="B29">
-        <v>22.988580604401</v>
+        <v>21.9084858554938</v>
       </c>
       <c r="C29">
-        <v>26.0400285098373</v>
+        <v>24.8165646284054</v>
       </c>
       <c r="D29">
-        <v>20.2068965887354</v>
+        <v>19.2574963942308</v>
       </c>
       <c r="E29">
-        <v>17.4110839928894</v>
+        <v>16.5930421695546</v>
       </c>
       <c r="F29">
-        <v>19.9303559350693</v>
+        <v>15.6715543108557</v>
       </c>
       <c r="G29">
-        <v>16.4441665137261</v>
+        <v>18.9939487179487</v>
       </c>
       <c r="H29">
-        <v>17.1092155570713</v>
+        <v>16.3053567108415</v>
       </c>
       <c r="I29">
-        <v>17.2070725527735</v>
+        <v>16.0811707142887</v>
       </c>
       <c r="J29">
-        <v>16.8739771254368</v>
+        <v>16.398615996532</v>
       </c>
       <c r="K29">
-        <v>19.795742065551</v>
+        <v>18.8656595422468</v>
       </c>
       <c r="L29">
-        <v>25.0681150318361</v>
+        <v>23.890315502721</v>
       </c>
     </row>
     <row r="30">
@@ -1505,37 +1505,37 @@
         <v>2007</v>
       </c>
       <c r="B30">
-        <v>23.326006395101</v>
+        <v>22.2900122919718</v>
       </c>
       <c r="C30">
-        <v>26.3603606062553</v>
+        <v>25.1895996246338</v>
       </c>
       <c r="D30">
-        <v>20.8222640434875</v>
+        <v>19.8974703862508</v>
       </c>
       <c r="E30">
-        <v>18.7117066707944</v>
+        <v>17.8806506622315</v>
       </c>
       <c r="F30">
-        <v>20.1748906166606</v>
+        <v>16.7028691492716</v>
       </c>
       <c r="G30">
-        <v>17.4791842861733</v>
+        <v>19.2788492045085</v>
       </c>
       <c r="H30">
-        <v>17.2799338341073</v>
+        <v>16.512468145752</v>
       </c>
       <c r="I30">
-        <v>17.4246152785608</v>
+        <v>16.2715200887044</v>
       </c>
       <c r="J30">
-        <v>17.0277870050272</v>
+        <v>16.6507237528483</v>
       </c>
       <c r="K30">
-        <v>20.2539343929573</v>
+        <v>19.3543823547363</v>
       </c>
       <c r="L30">
-        <v>25.2497623751564</v>
+        <v>24.1283271631877</v>
       </c>
     </row>
     <row r="31">
@@ -1543,37 +1543,37 @@
         <v>2008</v>
       </c>
       <c r="B31">
-        <v>23.121534032562</v>
+        <v>22.1331452166689</v>
       </c>
       <c r="C31">
-        <v>25.7279058466084</v>
+        <v>24.6281010343791</v>
       </c>
       <c r="D31">
-        <v>20.752978122559</v>
+        <v>19.865839256949</v>
       </c>
       <c r="E31">
-        <v>17.4868392189369</v>
+        <v>16.7393197729963</v>
       </c>
       <c r="F31">
-        <v>18.2773907536415</v>
+        <v>15.8061516779565</v>
       </c>
       <c r="G31">
-        <v>16.5119991021642</v>
+        <v>17.496077170418</v>
       </c>
       <c r="H31">
-        <v>16.0395819133713</v>
+        <v>15.3539291641873</v>
       </c>
       <c r="I31">
-        <v>16.2774223991404</v>
+        <v>15.0298032411042</v>
       </c>
       <c r="J31">
-        <v>15.700981660762</v>
+        <v>15.5816025530947</v>
       </c>
       <c r="K31">
-        <v>19.9090579297438</v>
+        <v>19.0579945805295</v>
       </c>
       <c r="L31">
-        <v>24.571281466928</v>
+        <v>23.5209195073854</v>
       </c>
     </row>
     <row r="32">
@@ -1581,37 +1581,37 @@
         <v>2009</v>
       </c>
       <c r="B32">
-        <v>23.3542660572887</v>
+        <v>22.3679613449922</v>
       </c>
       <c r="C32">
-        <v>26.5790154754377</v>
+        <v>25.4565221310816</v>
       </c>
       <c r="D32">
-        <v>21.1146997943317</v>
+        <v>20.2229771491074</v>
       </c>
       <c r="E32">
-        <v>19.0443595977749</v>
+        <v>18.2400722111416</v>
       </c>
       <c r="F32">
-        <v>21.4569431204322</v>
+        <v>17.8174210676019</v>
       </c>
       <c r="G32">
-        <v>18.6030718512788</v>
+        <v>20.5507667473769</v>
       </c>
       <c r="H32">
-        <v>17.9303621510911</v>
+        <v>17.1731214551333</v>
       </c>
       <c r="I32">
-        <v>17.7475373707842</v>
+        <v>17.5086900880088</v>
       </c>
       <c r="J32">
-        <v>18.2807275246619</v>
+        <v>16.9980177884721</v>
       </c>
       <c r="K32">
-        <v>20.7107117746533</v>
+        <v>19.8360504785866</v>
       </c>
       <c r="L32">
-        <v>25.5921839607076</v>
+        <v>24.5113667953775</v>
       </c>
     </row>
     <row r="33">
@@ -1619,37 +1619,37 @@
         <v>2010</v>
       </c>
       <c r="B33">
-        <v>23.9069402866471</v>
+        <v>22.9534282912722</v>
       </c>
       <c r="C33">
-        <v>26.4798426732486</v>
+        <v>25.4237122223484</v>
       </c>
       <c r="D33">
-        <v>21.5627970540426</v>
+        <v>20.7027796114782</v>
       </c>
       <c r="E33">
-        <v>19.2184802052973</v>
+        <v>18.4519642401045</v>
       </c>
       <c r="F33">
-        <v>20.0260476025289</v>
+        <v>18.1198265799747</v>
       </c>
       <c r="G33">
-        <v>18.8725451620912</v>
+        <v>19.2273223629119</v>
       </c>
       <c r="H33">
-        <v>17.5206223124635</v>
+        <v>16.8218242504339</v>
       </c>
       <c r="I33">
-        <v>18.7661039031543</v>
+        <v>14.391394173203</v>
       </c>
       <c r="J33">
-        <v>14.9892293549538</v>
+        <v>18.0176306579979</v>
       </c>
       <c r="K33">
-        <v>21.1710854975263</v>
+        <v>20.3266912030262</v>
       </c>
       <c r="L33">
-        <v>25.583339456173</v>
+        <v>24.5629654241671</v>
       </c>
     </row>
     <row r="34">
@@ -1657,37 +1657,37 @@
         <v>2011</v>
       </c>
       <c r="B34">
-        <v>22.8390630331906</v>
+        <v>21.9460921329218</v>
       </c>
       <c r="C34">
-        <v>24.6394769177292</v>
+        <v>23.6761127090749</v>
       </c>
       <c r="D34">
-        <v>21.5020454117746</v>
+        <v>20.6613497658512</v>
       </c>
       <c r="E34">
-        <v>17.2005152413339</v>
+        <v>16.5280025573495</v>
       </c>
       <c r="F34">
-        <v>18.6093182780526</v>
+        <v>16.2904414331149</v>
       </c>
       <c r="G34">
-        <v>16.9532879236973</v>
+        <v>17.8817236445954</v>
       </c>
       <c r="H34">
-        <v>15.695287733367</v>
+        <v>15.081627041732</v>
       </c>
       <c r="I34">
-        <v>15.8236665725708</v>
+        <v>14.7353184682485</v>
       </c>
       <c r="J34">
-        <v>15.3348881100163</v>
+        <v>15.2049864732897</v>
       </c>
       <c r="K34">
-        <v>20.9058008627458</v>
+        <v>20.088417426739</v>
       </c>
       <c r="L34">
-        <v>23.5846151597572</v>
+        <v>22.6624943616712</v>
       </c>
     </row>
     <row r="35">
@@ -1695,37 +1695,37 @@
         <v>2012</v>
       </c>
       <c r="B35">
-        <v>22.9499892828973</v>
+        <v>22.0873854596687</v>
       </c>
       <c r="C35">
-        <v>25.9972588150464</v>
+        <v>25.0201195854418</v>
       </c>
       <c r="D35">
-        <v>20.4049124453039</v>
+        <v>19.6379684929125</v>
       </c>
       <c r="E35">
-        <v>15.6843649014127</v>
+        <v>15.094848585649</v>
       </c>
       <c r="F35">
-        <v>18.8343557712762</v>
+        <v>14.4816930935021</v>
       </c>
       <c r="G35">
-        <v>15.0472631494098</v>
+        <v>18.1264431402033</v>
       </c>
       <c r="H35">
-        <v>15.4435738529286</v>
+        <v>14.8631079674923</v>
       </c>
       <c r="I35">
-        <v>16.6201716440302</v>
+        <v>13.3125333635735</v>
       </c>
       <c r="J35">
-        <v>13.8324428928043</v>
+        <v>15.995481870709</v>
       </c>
       <c r="K35">
-        <v>19.4650860999026</v>
+        <v>18.7334666868268</v>
       </c>
       <c r="L35">
-        <v>24.2756602614808</v>
+        <v>23.3632294496478</v>
       </c>
     </row>
     <row r="36">
@@ -1733,37 +1733,37 @@
         <v>2013</v>
       </c>
       <c r="B36">
-        <v>23.6795853508843</v>
+        <v>22.8574871716528</v>
       </c>
       <c r="C36">
-        <v>25.8924315352189</v>
+        <v>24.9935086653475</v>
       </c>
       <c r="D36">
-        <v>20.9564824606243</v>
+        <v>20.2289238560842</v>
       </c>
       <c r="E36">
-        <v>15.5302630753545</v>
+        <v>14.9910897406847</v>
       </c>
       <c r="F36">
-        <v>15.9116227863825</v>
+        <v>14.4637125250537</v>
       </c>
       <c r="G36">
-        <v>14.9839180770673</v>
+        <v>15.3592095609197</v>
       </c>
       <c r="H36">
-        <v>16.4963741678941</v>
+        <v>15.9236597826381</v>
       </c>
       <c r="I36">
-        <v>17.6892997340152</v>
+        <v>14.1634729542989</v>
       </c>
       <c r="J36">
-        <v>14.6728800137838</v>
+        <v>17.0751698458552</v>
       </c>
       <c r="K36">
-        <v>19.9578215239341</v>
+        <v>19.2649340221839</v>
       </c>
       <c r="L36">
-        <v>24.4948441076</v>
+        <v>23.6444421076061</v>
       </c>
     </row>
     <row r="37">
@@ -1771,37 +1771,37 @@
         <v>2014</v>
       </c>
       <c r="B37">
-        <v>23.6135447817285</v>
+        <v>22.848691068417</v>
       </c>
       <c r="C37">
-        <v>25.7118472745784</v>
+        <v>24.8790285662549</v>
       </c>
       <c r="D37">
-        <v>20.6989448715772</v>
+        <v>20.0284964068086</v>
       </c>
       <c r="E37">
-        <v>18.5500143984799</v>
+        <v>17.9491707925832</v>
       </c>
       <c r="F37">
-        <v>20.0717284894038</v>
+        <v>16.2992421320954</v>
       </c>
       <c r="G37">
-        <v>16.84485482525</v>
+        <v>19.4215958553751</v>
       </c>
       <c r="H37">
-        <v>17.9278030496992</v>
+        <v>17.3471131591797</v>
       </c>
       <c r="I37">
-        <v>18.5597512198825</v>
+        <v>15.5659390977247</v>
       </c>
       <c r="J37">
-        <v>16.0870046714342</v>
+        <v>17.9585922338056</v>
       </c>
       <c r="K37">
-        <v>19.9116663676348</v>
+        <v>19.2667182202779</v>
       </c>
       <c r="L37">
-        <v>24.6699227976806</v>
+        <v>23.8708525084323</v>
       </c>
     </row>
     <row r="38">
@@ -1809,37 +1809,37 @@
         <v>2015</v>
       </c>
       <c r="B38">
-        <v>23.5195784715274</v>
+        <v>22.8138765663587</v>
       </c>
       <c r="C38">
-        <v>26.1311461136254</v>
+        <v>25.3470844596739</v>
       </c>
       <c r="D38">
-        <v>21.0956362434889</v>
+        <v>20.4626644108602</v>
       </c>
       <c r="E38">
-        <v>17.1806731417095</v>
+        <v>16.6651692697815</v>
       </c>
       <c r="F38">
-        <v>18.0407401032055</v>
+        <v>15.7635444544196</v>
       </c>
       <c r="G38">
-        <v>16.2511583556056</v>
+        <v>17.4994300335162</v>
       </c>
       <c r="H38">
-        <v>16.5721818820998</v>
+        <v>16.0749357115888</v>
       </c>
       <c r="I38">
-        <v>19.1458799398873</v>
+        <v>13.2616130280037</v>
       </c>
       <c r="J38">
-        <v>13.6718346557157</v>
+        <v>18.5714102925648</v>
       </c>
       <c r="K38">
-        <v>20.1735458927116</v>
+        <v>19.5682412616048</v>
       </c>
       <c r="L38">
-        <v>24.8244538034751</v>
+        <v>24.0795992830127</v>
       </c>
     </row>
     <row r="39">
@@ -1847,37 +1847,37 @@
         <v>2016</v>
       </c>
       <c r="B39">
-        <v>24.1250522228596</v>
+        <v>23.4952939445976</v>
       </c>
       <c r="C39">
-        <v>26.6871542292658</v>
+        <v>25.9905150616536</v>
       </c>
       <c r="D39">
-        <v>21.3360226032685</v>
+        <v>20.7790689131596</v>
       </c>
       <c r="E39">
-        <v>19.5897484569052</v>
+        <v>19.0783793561944</v>
       </c>
       <c r="F39">
-        <v>19.1653525977989</v>
+        <v>19.9546923394713</v>
       </c>
       <c r="G39">
-        <v>20.4895497760535</v>
+        <v>18.6650618899165</v>
       </c>
       <c r="H39">
-        <v>19.0867116378278</v>
+        <v>18.5884737667681</v>
       </c>
       <c r="I39">
-        <v>19.7098019496113</v>
+        <v>16.9216515568165</v>
       </c>
       <c r="J39">
-        <v>17.3752126050374</v>
+        <v>19.1952989829023</v>
       </c>
       <c r="K39">
-        <v>20.8590048213665</v>
+        <v>20.3145031622109</v>
       </c>
       <c r="L39">
-        <v>25.9084682318629</v>
+        <v>25.2321558162304</v>
       </c>
     </row>
     <row r="40">
@@ -1885,37 +1885,37 @@
         <v>2017</v>
       </c>
       <c r="B40">
-        <v>24.1031561022231</v>
+        <v>23.5590687124129</v>
       </c>
       <c r="C40">
-        <v>26.2283967304256</v>
+        <v>25.6363356801863</v>
       </c>
       <c r="D40">
-        <v>21.9597128990654</v>
+        <v>21.4640100615796</v>
       </c>
       <c r="E40">
-        <v>20.9173742691874</v>
+        <v>20.4452004376967</v>
       </c>
       <c r="F40">
-        <v>21.2244704945564</v>
+        <v>20.3204856826453</v>
       </c>
       <c r="G40">
-        <v>20.7897792761107</v>
+        <v>20.745364492732</v>
       </c>
       <c r="H40">
-        <v>16.7978767008044</v>
+        <v>16.4186934581729</v>
       </c>
       <c r="I40">
-        <v>18.3180882564823</v>
+        <v>15.0025655535142</v>
       </c>
       <c r="J40">
-        <v>15.349043881334</v>
+        <v>17.9045888465497</v>
       </c>
       <c r="K40">
-        <v>21.0986261370445</v>
+        <v>20.6223608556514</v>
       </c>
       <c r="L40">
-        <v>25.3506934493904</v>
+        <v>24.7784450446479</v>
       </c>
     </row>
     <row r="41">
@@ -1923,37 +1923,37 @@
         <v>2018</v>
       </c>
       <c r="B41">
-        <v>24.3588728944773</v>
+        <v>23.9089083436178</v>
       </c>
       <c r="C41">
-        <v>27.110610159391</v>
+        <v>26.6098146760884</v>
       </c>
       <c r="D41">
-        <v>21.712313476083</v>
+        <v>21.3112369803145</v>
       </c>
       <c r="E41">
-        <v>16.6396999901725</v>
+        <v>16.3323263622978</v>
       </c>
       <c r="F41">
-        <v>17.791025415729</v>
+        <v>15.8263695720893</v>
       </c>
       <c r="G41">
-        <v>16.1242211165386</v>
+        <v>17.4623841524326</v>
       </c>
       <c r="H41">
-        <v>16.790842590084</v>
+        <v>16.4806770098731</v>
       </c>
       <c r="I41">
-        <v>17.6554457742778</v>
+        <v>15.0539915373766</v>
       </c>
       <c r="J41">
-        <v>15.3373069628827</v>
+        <v>17.3293089795886</v>
       </c>
       <c r="K41">
-        <v>20.3286355209041</v>
+        <v>19.9531187475551</v>
       </c>
       <c r="L41">
-        <v>25.4581635898124</v>
+        <v>24.9878926049839</v>
       </c>
     </row>
     <row r="42">
@@ -1961,37 +1961,37 @@
         <v>2019</v>
       </c>
       <c r="B42">
-        <v>24.7746210595659</v>
+        <v>24.3970741306965</v>
       </c>
       <c r="C42">
-        <v>27.6277496206944</v>
+        <v>27.2067231195912</v>
       </c>
       <c r="D42">
-        <v>22.264195876657</v>
+        <v>21.924905973624</v>
       </c>
       <c r="E42">
-        <v>18.8544438531134</v>
+        <v>18.5671160528145</v>
       </c>
       <c r="F42">
-        <v>20.848190526876</v>
+        <v>17.2775984986115</v>
       </c>
       <c r="G42">
-        <v>17.5449708981232</v>
+        <v>20.5304794996525</v>
       </c>
       <c r="H42">
-        <v>18.5236295301144</v>
+        <v>18.2413430957913</v>
       </c>
       <c r="I42">
-        <v>18.9824373916212</v>
+        <v>17.5759187453683</v>
       </c>
       <c r="J42">
-        <v>17.8479076776814</v>
+        <v>18.6931590643187</v>
       </c>
       <c r="K42">
-        <v>21.4249618158751</v>
+        <v>21.0984612201534</v>
       </c>
       <c r="L42">
-        <v>25.9233095190384</v>
+        <v>25.528257426354</v>
       </c>
     </row>
     <row r="43">
@@ -1999,37 +1999,37 @@
         <v>2020</v>
       </c>
       <c r="B43">
-        <v>25.6154797357671</v>
+        <v>25.297043678672</v>
       </c>
       <c r="C43">
-        <v>27.5804683766445</v>
+        <v>27.2376047764585</v>
       </c>
       <c r="D43">
-        <v>23.0223706114192</v>
+        <v>22.736170509055</v>
       </c>
       <c r="E43">
-        <v>19.9502317394529</v>
+        <v>19.7022225981533</v>
       </c>
       <c r="F43">
-        <v>19.3742317912959</v>
+        <v>20.3600010956104</v>
       </c>
       <c r="G43">
-        <v>20.6162902712822</v>
+        <v>19.1333831308567</v>
       </c>
       <c r="H43">
-        <v>20.7459426927967</v>
+        <v>20.488041757114</v>
       </c>
       <c r="I43">
-        <v>21.4207457093632</v>
+        <v>19.5639855335765</v>
       </c>
       <c r="J43">
-        <v>19.8102545638044</v>
+        <v>21.1544560331951</v>
       </c>
       <c r="K43">
-        <v>22.3597376336571</v>
+        <v>22.0817749812613</v>
       </c>
       <c r="L43">
-        <v>26.6314008681714</v>
+        <v>26.3003354977446</v>
       </c>
     </row>
     <row r="44">
@@ -2037,37 +2037,37 @@
         <v>2021</v>
       </c>
       <c r="B44">
-        <v>25.9361471991262</v>
+        <v>25.7023577724153</v>
       </c>
       <c r="C44">
-        <v>26.9734008493787</v>
+        <v>26.7302615784374</v>
       </c>
       <c r="D44">
-        <v>24.1345752169469</v>
+        <v>23.9170252292575</v>
       </c>
       <c r="E44">
-        <v>20.3289836848189</v>
+        <v>20.1457374453215</v>
       </c>
       <c r="F44">
-        <v>20.442765404084</v>
+        <v>20.0024076757877</v>
       </c>
       <c r="G44">
-        <v>20.1843501833494</v>
+        <v>20.2584935318004</v>
       </c>
       <c r="H44">
-        <v>18.6645165330661</v>
+        <v>18.4962738643845</v>
       </c>
       <c r="I44">
-        <v>19.9509896663482</v>
+        <v>17.963544551003</v>
       </c>
       <c r="J44">
-        <v>18.1269414976747</v>
+        <v>19.771150679447</v>
       </c>
       <c r="K44">
-        <v>23.0175406708268</v>
+        <v>22.8100596754264</v>
       </c>
       <c r="L44">
-        <v>26.3293186839453</v>
+        <v>26.0919851943739</v>
       </c>
     </row>
     <row r="45">
@@ -2075,37 +2075,37 @@
         <v>2022</v>
       </c>
       <c r="B45">
-        <v>24.5455608986758</v>
+        <v>24.4121036363522</v>
       </c>
       <c r="C45">
-        <v>26.8197635814185</v>
+        <v>26.6739411967308</v>
       </c>
       <c r="D45">
-        <v>22.3220363630204</v>
+        <v>22.2006686796827</v>
       </c>
       <c r="E45">
-        <v>21.0069171600519</v>
+        <v>20.8926999431134</v>
       </c>
       <c r="F45">
-        <v>22.8154161238864</v>
+        <v>18.1648899755501</v>
       </c>
       <c r="G45">
-        <v>18.2641946697567</v>
+        <v>22.691365873528</v>
       </c>
       <c r="H45">
-        <v>20.241529502294</v>
+        <v>20.1314737930857</v>
       </c>
       <c r="I45">
-        <v>20.3006952491309</v>
+        <v>19.9840438633851</v>
       </c>
       <c r="J45">
-        <v>20.0932935955626</v>
+        <v>20.1903178484108</v>
       </c>
       <c r="K45">
-        <v>21.7513630359778</v>
+        <v>21.6330981743773</v>
       </c>
       <c r="L45">
-        <v>26.0331417141204</v>
+        <v>25.8915962901967</v>
       </c>
     </row>
     <row r="46">
@@ -2113,37 +2113,37 @@
         <v>2023</v>
       </c>
       <c r="B46">
-        <v>25.2341974994108</v>
+        <v>25.1484798591165</v>
       </c>
       <c r="C46">
-        <v>27.4639975528475</v>
+        <v>27.3707055405561</v>
       </c>
       <c r="D46">
-        <v>23.1963040062985</v>
+        <v>23.117508853688</v>
       </c>
       <c r="E46">
-        <v>20.5802704500987</v>
+        <v>20.510361659869</v>
       </c>
       <c r="F46">
-        <v>20.5802704500987</v>
+        <v>21.1024</v>
       </c>
       <c r="G46">
-        <v>21.1743267304696</v>
+        <v>20.510361659869</v>
       </c>
       <c r="H46">
-        <v>18.8376364802402</v>
+        <v>18.7736472153608</v>
       </c>
       <c r="I46">
-        <v>19.6199643890496</v>
+        <v>18.4608215044807</v>
       </c>
       <c r="J46">
-        <v>18.5237445147829</v>
+        <v>19.5533176470588</v>
       </c>
       <c r="K46">
-        <v>22.7205982777103</v>
+        <v>22.6434190422507</v>
       </c>
       <c r="L46">
-        <v>26.0551956833908</v>
+        <v>25.9666892075483</v>
       </c>
     </row>
     <row r="47">
@@ -2163,19 +2163,19 @@
         <v>20.2480000305176</v>
       </c>
       <c r="F47">
+        <v>20.2919998931885</v>
+      </c>
+      <c r="G47">
         <v>19.9319997406006</v>
-      </c>
-      <c r="G47">
-        <v>20.2919998931885</v>
       </c>
       <c r="H47">
         <v>18.1920000457764</v>
       </c>
       <c r="I47">
+        <v>17.5700000762939</v>
+      </c>
+      <c r="J47">
         <v>18.5600000762939</v>
-      </c>
-      <c r="J47">
-        <v>17.5700000762939</v>
       </c>
       <c r="K47">
         <v>22.9788890075684</v>
@@ -2224,14 +2224,14 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Black Women</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Black Men</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Black Women</t>
-        </is>
-      </c>
       <c r="H1" t="inlineStr">
         <is>
           <t>Hispanic</t>
@@ -2239,12 +2239,12 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Hispanic Women</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Hispanic Men</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Hispanic Women</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2275,19 +2275,19 @@
         <v>98</v>
       </c>
       <c r="F2">
+        <v>47</v>
+      </c>
+      <c r="G2">
         <v>51</v>
-      </c>
-      <c r="G2">
-        <v>47</v>
       </c>
       <c r="H2">
         <v>30</v>
       </c>
       <c r="I2">
+        <v>11</v>
+      </c>
+      <c r="J2">
         <v>19</v>
-      </c>
-      <c r="J2">
-        <v>11</v>
       </c>
       <c r="K2">
         <v>1524</v>
@@ -2313,19 +2313,19 @@
         <v>92</v>
       </c>
       <c r="F3">
+        <v>45</v>
+      </c>
+      <c r="G3">
         <v>47</v>
-      </c>
-      <c r="G3">
-        <v>45</v>
       </c>
       <c r="H3">
         <v>31</v>
       </c>
       <c r="I3">
+        <v>16</v>
+      </c>
+      <c r="J3">
         <v>15</v>
-      </c>
-      <c r="J3">
-        <v>16</v>
       </c>
       <c r="K3">
         <v>1527</v>
@@ -2351,19 +2351,19 @@
         <v>82</v>
       </c>
       <c r="F4">
+        <v>36</v>
+      </c>
+      <c r="G4">
         <v>46</v>
-      </c>
-      <c r="G4">
-        <v>36</v>
       </c>
       <c r="H4">
         <v>34</v>
       </c>
       <c r="I4">
+        <v>12</v>
+      </c>
+      <c r="J4">
         <v>22</v>
-      </c>
-      <c r="J4">
-        <v>12</v>
       </c>
       <c r="K4">
         <v>1513</v>
@@ -2398,10 +2398,10 @@
         <v>35</v>
       </c>
       <c r="I5">
+        <v>16</v>
+      </c>
+      <c r="J5">
         <v>19</v>
-      </c>
-      <c r="J5">
-        <v>16</v>
       </c>
       <c r="K5">
         <v>1495</v>
@@ -2427,19 +2427,19 @@
         <v>83</v>
       </c>
       <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6">
         <v>34</v>
-      </c>
-      <c r="G6">
-        <v>49</v>
       </c>
       <c r="H6">
         <v>22</v>
       </c>
       <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
         <v>12</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
       </c>
       <c r="K6">
         <v>1484</v>
@@ -2465,19 +2465,19 @@
         <v>64</v>
       </c>
       <c r="F7">
+        <v>35</v>
+      </c>
+      <c r="G7">
         <v>29</v>
-      </c>
-      <c r="G7">
-        <v>35</v>
       </c>
       <c r="H7">
         <v>23</v>
       </c>
       <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
         <v>14</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
       </c>
       <c r="K7">
         <v>1385</v>
@@ -2503,19 +2503,19 @@
         <v>84</v>
       </c>
       <c r="F8">
+        <v>48</v>
+      </c>
+      <c r="G8">
         <v>36</v>
-      </c>
-      <c r="G8">
-        <v>48</v>
       </c>
       <c r="H8">
         <v>18</v>
       </c>
       <c r="I8">
+        <v>3</v>
+      </c>
+      <c r="J8">
         <v>15</v>
-      </c>
-      <c r="J8">
-        <v>3</v>
       </c>
       <c r="K8">
         <v>1264</v>
@@ -2541,19 +2541,19 @@
         <v>81</v>
       </c>
       <c r="F9">
+        <v>44</v>
+      </c>
+      <c r="G9">
         <v>37</v>
-      </c>
-      <c r="G9">
-        <v>44</v>
       </c>
       <c r="H9">
         <v>11</v>
       </c>
       <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9">
         <v>6</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
       </c>
       <c r="K9">
         <v>1203</v>
@@ -2617,19 +2617,19 @@
         <v>81</v>
       </c>
       <c r="F11">
+        <v>39</v>
+      </c>
+      <c r="G11">
         <v>42</v>
-      </c>
-      <c r="G11">
-        <v>39</v>
       </c>
       <c r="H11">
         <v>23</v>
       </c>
       <c r="I11">
+        <v>12</v>
+      </c>
+      <c r="J11">
         <v>11</v>
-      </c>
-      <c r="J11">
-        <v>12</v>
       </c>
       <c r="K11">
         <v>1325</v>
@@ -2655,19 +2655,19 @@
         <v>76</v>
       </c>
       <c r="F12">
+        <v>44</v>
+      </c>
+      <c r="G12">
         <v>32</v>
-      </c>
-      <c r="G12">
-        <v>44</v>
       </c>
       <c r="H12">
         <v>25</v>
       </c>
       <c r="I12">
+        <v>12</v>
+      </c>
+      <c r="J12">
         <v>13</v>
-      </c>
-      <c r="J12">
-        <v>12</v>
       </c>
       <c r="K12">
         <v>1488</v>
@@ -2693,19 +2693,19 @@
         <v>98</v>
       </c>
       <c r="F13">
+        <v>52</v>
+      </c>
+      <c r="G13">
         <v>46</v>
-      </c>
-      <c r="G13">
-        <v>52</v>
       </c>
       <c r="H13">
         <v>19</v>
       </c>
       <c r="I13">
+        <v>10</v>
+      </c>
+      <c r="J13">
         <v>9</v>
-      </c>
-      <c r="J13">
-        <v>10</v>
       </c>
       <c r="K13">
         <v>1537</v>
@@ -2731,19 +2731,19 @@
         <v>100</v>
       </c>
       <c r="F14">
+        <v>54</v>
+      </c>
+      <c r="G14">
         <v>46</v>
-      </c>
-      <c r="G14">
-        <v>54</v>
       </c>
       <c r="H14">
         <v>14</v>
       </c>
       <c r="I14">
+        <v>10</v>
+      </c>
+      <c r="J14">
         <v>4</v>
-      </c>
-      <c r="J14">
-        <v>10</v>
       </c>
       <c r="K14">
         <v>1527</v>
@@ -2769,19 +2769,19 @@
         <v>95</v>
       </c>
       <c r="F15">
+        <v>53</v>
+      </c>
+      <c r="G15">
         <v>42</v>
-      </c>
-      <c r="G15">
-        <v>53</v>
       </c>
       <c r="H15">
         <v>36</v>
       </c>
       <c r="I15">
+        <v>17</v>
+      </c>
+      <c r="J15">
         <v>19</v>
-      </c>
-      <c r="J15">
-        <v>17</v>
       </c>
       <c r="K15">
         <v>1521</v>
@@ -2807,19 +2807,19 @@
         <v>95</v>
       </c>
       <c r="F16">
+        <v>57</v>
+      </c>
+      <c r="G16">
         <v>38</v>
-      </c>
-      <c r="G16">
-        <v>57</v>
       </c>
       <c r="H16">
         <v>39</v>
       </c>
       <c r="I16">
+        <v>19</v>
+      </c>
+      <c r="J16">
         <v>20</v>
-      </c>
-      <c r="J16">
-        <v>19</v>
       </c>
       <c r="K16">
         <v>1562</v>
@@ -2845,19 +2845,19 @@
         <v>87</v>
       </c>
       <c r="F17">
+        <v>48</v>
+      </c>
+      <c r="G17">
         <v>39</v>
-      </c>
-      <c r="G17">
-        <v>48</v>
       </c>
       <c r="H17">
         <v>26</v>
       </c>
       <c r="I17">
+        <v>14</v>
+      </c>
+      <c r="J17">
         <v>12</v>
-      </c>
-      <c r="J17">
-        <v>14</v>
       </c>
       <c r="K17">
         <v>1310</v>
@@ -2883,19 +2883,19 @@
         <v>94</v>
       </c>
       <c r="F18">
+        <v>57</v>
+      </c>
+      <c r="G18">
         <v>37</v>
-      </c>
-      <c r="G18">
-        <v>57</v>
       </c>
       <c r="H18">
         <v>41</v>
       </c>
       <c r="I18">
+        <v>17</v>
+      </c>
+      <c r="J18">
         <v>24</v>
-      </c>
-      <c r="J18">
-        <v>17</v>
       </c>
       <c r="K18">
         <v>1259</v>
@@ -2921,19 +2921,19 @@
         <v>91</v>
       </c>
       <c r="F19">
+        <v>53</v>
+      </c>
+      <c r="G19">
         <v>38</v>
-      </c>
-      <c r="G19">
-        <v>53</v>
       </c>
       <c r="H19">
         <v>38</v>
       </c>
       <c r="I19">
+        <v>16</v>
+      </c>
+      <c r="J19">
         <v>22</v>
-      </c>
-      <c r="J19">
-        <v>16</v>
       </c>
       <c r="K19">
         <v>1291</v>
@@ -2959,19 +2959,19 @@
         <v>79</v>
       </c>
       <c r="F20">
+        <v>43</v>
+      </c>
+      <c r="G20">
         <v>36</v>
-      </c>
-      <c r="G20">
-        <v>43</v>
       </c>
       <c r="H20">
         <v>56</v>
       </c>
       <c r="I20">
+        <v>23</v>
+      </c>
+      <c r="J20">
         <v>33</v>
-      </c>
-      <c r="J20">
-        <v>23</v>
       </c>
       <c r="K20">
         <v>1246</v>
@@ -2997,19 +2997,19 @@
         <v>81</v>
       </c>
       <c r="F21">
+        <v>48</v>
+      </c>
+      <c r="G21">
         <v>33</v>
-      </c>
-      <c r="G21">
-        <v>48</v>
       </c>
       <c r="H21">
         <v>43</v>
       </c>
       <c r="I21">
+        <v>18</v>
+      </c>
+      <c r="J21">
         <v>25</v>
-      </c>
-      <c r="J21">
-        <v>18</v>
       </c>
       <c r="K21">
         <v>1250</v>
@@ -3035,19 +3035,19 @@
         <v>102</v>
       </c>
       <c r="F22">
+        <v>59</v>
+      </c>
+      <c r="G22">
         <v>43</v>
-      </c>
-      <c r="G22">
-        <v>59</v>
       </c>
       <c r="H22">
         <v>41</v>
       </c>
       <c r="I22">
+        <v>14</v>
+      </c>
+      <c r="J22">
         <v>27</v>
-      </c>
-      <c r="J22">
-        <v>14</v>
       </c>
       <c r="K22">
         <v>1212</v>
@@ -3073,19 +3073,19 @@
         <v>104</v>
       </c>
       <c r="F23">
+        <v>61</v>
+      </c>
+      <c r="G23">
         <v>43</v>
-      </c>
-      <c r="G23">
-        <v>61</v>
       </c>
       <c r="H23">
         <v>88</v>
       </c>
       <c r="I23">
+        <v>31</v>
+      </c>
+      <c r="J23">
         <v>57</v>
-      </c>
-      <c r="J23">
-        <v>31</v>
       </c>
       <c r="K23">
         <v>1222</v>
@@ -3111,19 +3111,19 @@
         <v>121</v>
       </c>
       <c r="F24">
+        <v>79</v>
+      </c>
+      <c r="G24">
         <v>42</v>
-      </c>
-      <c r="G24">
-        <v>79</v>
       </c>
       <c r="H24">
         <v>139</v>
       </c>
       <c r="I24">
+        <v>47</v>
+      </c>
+      <c r="J24">
         <v>92</v>
-      </c>
-      <c r="J24">
-        <v>47</v>
       </c>
       <c r="K24">
         <v>1632</v>
@@ -3149,19 +3149,19 @@
         <v>122</v>
       </c>
       <c r="F25">
+        <v>78</v>
+      </c>
+      <c r="G25">
         <v>44</v>
-      </c>
-      <c r="G25">
-        <v>78</v>
       </c>
       <c r="H25">
         <v>168</v>
       </c>
       <c r="I25">
+        <v>68</v>
+      </c>
+      <c r="J25">
         <v>100</v>
-      </c>
-      <c r="J25">
-        <v>68</v>
       </c>
       <c r="K25">
         <v>1954</v>
@@ -3187,19 +3187,19 @@
         <v>127</v>
       </c>
       <c r="F26">
+        <v>76</v>
+      </c>
+      <c r="G26">
         <v>51</v>
-      </c>
-      <c r="G26">
-        <v>76</v>
       </c>
       <c r="H26">
         <v>162</v>
       </c>
       <c r="I26">
+        <v>62</v>
+      </c>
+      <c r="J26">
         <v>100</v>
-      </c>
-      <c r="J26">
-        <v>62</v>
       </c>
       <c r="K26">
         <v>2012</v>
@@ -3225,19 +3225,19 @@
         <v>115</v>
       </c>
       <c r="F27">
+        <v>59</v>
+      </c>
+      <c r="G27">
         <v>56</v>
-      </c>
-      <c r="G27">
-        <v>59</v>
       </c>
       <c r="H27">
         <v>197</v>
       </c>
       <c r="I27">
+        <v>76</v>
+      </c>
+      <c r="J27">
         <v>121</v>
-      </c>
-      <c r="J27">
-        <v>76</v>
       </c>
       <c r="K27">
         <v>1921</v>
@@ -3263,19 +3263,19 @@
         <v>129</v>
       </c>
       <c r="F28">
+        <v>77</v>
+      </c>
+      <c r="G28">
         <v>52</v>
-      </c>
-      <c r="G28">
-        <v>77</v>
       </c>
       <c r="H28">
         <v>159</v>
       </c>
       <c r="I28">
+        <v>66</v>
+      </c>
+      <c r="J28">
         <v>93</v>
-      </c>
-      <c r="J28">
-        <v>66</v>
       </c>
       <c r="K28">
         <v>1821</v>
@@ -3301,19 +3301,19 @@
         <v>123</v>
       </c>
       <c r="F29">
+        <v>72</v>
+      </c>
+      <c r="G29">
         <v>51</v>
-      </c>
-      <c r="G29">
-        <v>72</v>
       </c>
       <c r="H29">
         <v>141</v>
       </c>
       <c r="I29">
+        <v>60</v>
+      </c>
+      <c r="J29">
         <v>81</v>
-      </c>
-      <c r="J29">
-        <v>60</v>
       </c>
       <c r="K29">
         <v>1800</v>
@@ -3339,19 +3339,19 @@
         <v>142</v>
       </c>
       <c r="F30">
+        <v>84</v>
+      </c>
+      <c r="G30">
         <v>58</v>
-      </c>
-      <c r="G30">
-        <v>84</v>
       </c>
       <c r="H30">
         <v>156</v>
       </c>
       <c r="I30">
+        <v>67</v>
+      </c>
+      <c r="J30">
         <v>89</v>
-      </c>
-      <c r="J30">
-        <v>67</v>
       </c>
       <c r="K30">
         <v>1814</v>
@@ -3377,19 +3377,19 @@
         <v>152</v>
       </c>
       <c r="F31">
+        <v>97</v>
+      </c>
+      <c r="G31">
         <v>55</v>
-      </c>
-      <c r="G31">
-        <v>97</v>
       </c>
       <c r="H31">
         <v>177</v>
       </c>
       <c r="I31">
+        <v>66</v>
+      </c>
+      <c r="J31">
         <v>111</v>
-      </c>
-      <c r="J31">
-        <v>66</v>
       </c>
       <c r="K31">
         <v>1873</v>
@@ -3415,19 +3415,19 @@
         <v>119</v>
       </c>
       <c r="F32">
+        <v>78</v>
+      </c>
+      <c r="G32">
         <v>41</v>
-      </c>
-      <c r="G32">
-        <v>78</v>
       </c>
       <c r="H32">
         <v>166</v>
       </c>
       <c r="I32">
+        <v>65</v>
+      </c>
+      <c r="J32">
         <v>101</v>
-      </c>
-      <c r="J32">
-        <v>65</v>
       </c>
       <c r="K32">
         <v>1830</v>
@@ -3453,19 +3453,19 @@
         <v>155</v>
       </c>
       <c r="F33">
+        <v>88</v>
+      </c>
+      <c r="G33">
         <v>67</v>
-      </c>
-      <c r="G33">
-        <v>88</v>
       </c>
       <c r="H33">
         <v>179</v>
       </c>
       <c r="I33">
+        <v>72</v>
+      </c>
+      <c r="J33">
         <v>107</v>
-      </c>
-      <c r="J33">
-        <v>72</v>
       </c>
       <c r="K33">
         <v>1791</v>
@@ -3491,19 +3491,19 @@
         <v>124</v>
       </c>
       <c r="F34">
+        <v>76</v>
+      </c>
+      <c r="G34">
         <v>48</v>
-      </c>
-      <c r="G34">
-        <v>76</v>
       </c>
       <c r="H34">
         <v>173</v>
       </c>
       <c r="I34">
+        <v>71</v>
+      </c>
+      <c r="J34">
         <v>102</v>
-      </c>
-      <c r="J34">
-        <v>71</v>
       </c>
       <c r="K34">
         <v>1797</v>
@@ -3529,19 +3529,19 @@
         <v>137</v>
       </c>
       <c r="F35">
+        <v>87</v>
+      </c>
+      <c r="G35">
         <v>50</v>
-      </c>
-      <c r="G35">
-        <v>87</v>
       </c>
       <c r="H35">
         <v>172</v>
       </c>
       <c r="I35">
+        <v>66</v>
+      </c>
+      <c r="J35">
         <v>106</v>
-      </c>
-      <c r="J35">
-        <v>66</v>
       </c>
       <c r="K35">
         <v>1771</v>
@@ -3567,19 +3567,19 @@
         <v>128</v>
       </c>
       <c r="F36">
+        <v>65</v>
+      </c>
+      <c r="G36">
         <v>63</v>
-      </c>
-      <c r="G36">
-        <v>65</v>
       </c>
       <c r="H36">
         <v>169</v>
       </c>
       <c r="I36">
+        <v>80</v>
+      </c>
+      <c r="J36">
         <v>89</v>
-      </c>
-      <c r="J36">
-        <v>80</v>
       </c>
       <c r="K36">
         <v>1738</v>
@@ -3605,19 +3605,19 @@
         <v>132</v>
       </c>
       <c r="F37">
+        <v>67</v>
+      </c>
+      <c r="G37">
         <v>65</v>
-      </c>
-      <c r="G37">
-        <v>67</v>
       </c>
       <c r="H37">
         <v>142</v>
       </c>
       <c r="I37">
+        <v>65</v>
+      </c>
+      <c r="J37">
         <v>77</v>
-      </c>
-      <c r="J37">
-        <v>65</v>
       </c>
       <c r="K37">
         <v>1670</v>
@@ -3643,19 +3643,19 @@
         <v>128</v>
       </c>
       <c r="F38">
+        <v>69</v>
+      </c>
+      <c r="G38">
         <v>59</v>
-      </c>
-      <c r="G38">
-        <v>69</v>
       </c>
       <c r="H38">
         <v>151</v>
       </c>
       <c r="I38">
+        <v>71</v>
+      </c>
+      <c r="J38">
         <v>80</v>
-      </c>
-      <c r="J38">
-        <v>71</v>
       </c>
       <c r="K38">
         <v>1353</v>
@@ -3681,19 +3681,19 @@
         <v>106</v>
       </c>
       <c r="F39">
+        <v>63</v>
+      </c>
+      <c r="G39">
         <v>43</v>
-      </c>
-      <c r="G39">
-        <v>63</v>
       </c>
       <c r="H39">
         <v>170</v>
       </c>
       <c r="I39">
+        <v>78</v>
+      </c>
+      <c r="J39">
         <v>92</v>
-      </c>
-      <c r="J39">
-        <v>78</v>
       </c>
       <c r="K39">
         <v>1238</v>
@@ -3719,19 +3719,19 @@
         <v>126</v>
       </c>
       <c r="F40">
+        <v>77</v>
+      </c>
+      <c r="G40">
         <v>49</v>
-      </c>
-      <c r="G40">
-        <v>77</v>
       </c>
       <c r="H40">
         <v>150</v>
       </c>
       <c r="I40">
+        <v>73</v>
+      </c>
+      <c r="J40">
         <v>77</v>
-      </c>
-      <c r="J40">
-        <v>73</v>
       </c>
       <c r="K40">
         <v>1229</v>
@@ -3757,19 +3757,19 @@
         <v>114</v>
       </c>
       <c r="F41">
+        <v>72</v>
+      </c>
+      <c r="G41">
         <v>42</v>
-      </c>
-      <c r="G41">
-        <v>72</v>
       </c>
       <c r="H41">
         <v>120</v>
       </c>
       <c r="I41">
+        <v>53</v>
+      </c>
+      <c r="J41">
         <v>67</v>
-      </c>
-      <c r="J41">
-        <v>53</v>
       </c>
       <c r="K41">
         <v>1156</v>
@@ -3795,19 +3795,19 @@
         <v>113</v>
       </c>
       <c r="F42">
+        <v>61</v>
+      </c>
+      <c r="G42">
         <v>52</v>
-      </c>
-      <c r="G42">
-        <v>61</v>
       </c>
       <c r="H42">
         <v>128</v>
       </c>
       <c r="I42">
+        <v>52</v>
+      </c>
+      <c r="J42">
         <v>76</v>
-      </c>
-      <c r="J42">
-        <v>52</v>
       </c>
       <c r="K42">
         <v>1099</v>
@@ -3833,19 +3833,19 @@
         <v>96</v>
       </c>
       <c r="F43">
+        <v>47</v>
+      </c>
+      <c r="G43">
         <v>49</v>
-      </c>
-      <c r="G43">
-        <v>47</v>
       </c>
       <c r="H43">
         <v>93</v>
       </c>
       <c r="I43">
+        <v>39</v>
+      </c>
+      <c r="J43">
         <v>54</v>
-      </c>
-      <c r="J43">
-        <v>39</v>
       </c>
       <c r="K43">
         <v>968</v>
@@ -3871,19 +3871,19 @@
         <v>83</v>
       </c>
       <c r="F44">
+        <v>47</v>
+      </c>
+      <c r="G44">
         <v>36</v>
-      </c>
-      <c r="G44">
-        <v>47</v>
       </c>
       <c r="H44">
         <v>120</v>
       </c>
       <c r="I44">
+        <v>48</v>
+      </c>
+      <c r="J44">
         <v>72</v>
-      </c>
-      <c r="J44">
-        <v>48</v>
       </c>
       <c r="K44">
         <v>958</v>
@@ -3909,19 +3909,19 @@
         <v>76</v>
       </c>
       <c r="F45">
+        <v>42</v>
+      </c>
+      <c r="G45">
         <v>34</v>
-      </c>
-      <c r="G45">
-        <v>42</v>
       </c>
       <c r="H45">
         <v>121</v>
       </c>
       <c r="I45">
+        <v>46</v>
+      </c>
+      <c r="J45">
         <v>75</v>
-      </c>
-      <c r="J45">
-        <v>46</v>
       </c>
       <c r="K45">
         <v>916</v>
@@ -3947,19 +3947,19 @@
         <v>81</v>
       </c>
       <c r="F46">
+        <v>47</v>
+      </c>
+      <c r="G46">
         <v>34</v>
-      </c>
-      <c r="G46">
-        <v>47</v>
       </c>
       <c r="H46">
         <v>157</v>
       </c>
       <c r="I46">
+        <v>63</v>
+      </c>
+      <c r="J46">
         <v>94</v>
-      </c>
-      <c r="J46">
-        <v>63</v>
       </c>
       <c r="K46">
         <v>970</v>
@@ -3985,19 +3985,19 @@
         <v>76</v>
       </c>
       <c r="F47">
+        <v>40</v>
+      </c>
+      <c r="G47">
         <v>36</v>
-      </c>
-      <c r="G47">
-        <v>40</v>
       </c>
       <c r="H47">
         <v>133</v>
       </c>
       <c r="I47">
+        <v>57</v>
+      </c>
+      <c r="J47">
         <v>76</v>
-      </c>
-      <c r="J47">
-        <v>57</v>
       </c>
       <c r="K47">
         <v>986</v>
@@ -4063,167 +4063,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="B2">
         <v>1992</v>
       </c>
       <c r="C2">
-        <v>18.2615657520612</v>
+        <v>17.11094323932</v>
       </c>
       <c r="D2">
-        <v>634</v>
+        <v>1335</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="I2">
         <v>1992</v>
       </c>
       <c r="J2">
-        <v>18.2615657520612</v>
+        <v>17.11094323932</v>
       </c>
       <c r="K2">
-        <v>634</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="B3">
         <v>1992</v>
       </c>
       <c r="C3">
-        <v>18.3325391363223</v>
+        <v>17.0446991942064</v>
       </c>
       <c r="D3">
-        <v>1335</v>
+        <v>634</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="I3">
         <v>1992</v>
       </c>
       <c r="J3">
-        <v>18.3325391363223</v>
+        <v>17.0446991942064</v>
       </c>
       <c r="K3">
-        <v>1335</v>
+        <v>634</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="B4">
         <v>1992</v>
       </c>
       <c r="C4">
-        <v>31.2486273314398</v>
+        <v>11.5581132467738</v>
       </c>
       <c r="D4">
-        <v>649</v>
+        <v>376</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="I4">
         <v>1992</v>
       </c>
       <c r="J4">
-        <v>31.2486273314398</v>
+        <v>11.5581132467738</v>
       </c>
       <c r="K4">
-        <v>649</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate degree-all</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="B5">
         <v>1992</v>
       </c>
       <c r="C5">
-        <v>24.0538194123878</v>
+        <v>29.1663628588982</v>
       </c>
       <c r="D5">
-        <v>258</v>
+        <v>649</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Associate degree-occupational/vocational</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="I5">
         <v>1992</v>
       </c>
       <c r="J5">
-        <v>24.2249030621635</v>
+        <v>29.1663628588982</v>
       </c>
       <c r="K5">
-        <v>209</v>
+        <v>649</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Associate degree-all</t>
         </is>
       </c>
       <c r="B6">
         <v>1992</v>
       </c>
       <c r="C6">
-        <v>12.3832777933372</v>
+        <v>22.4509837722779</v>
       </c>
       <c r="D6">
-        <v>376</v>
+        <v>258</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Associate degree-occupational/vocational</t>
         </is>
       </c>
       <c r="I6">
         <v>1992</v>
       </c>
       <c r="J6">
-        <v>12.3832777933372</v>
+        <v>22.6106671963098</v>
       </c>
       <c r="K6">
-        <v>376</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="B7">
         <v>1993</v>
       </c>
       <c r="C7">
-        <v>31.705459221145</v>
+        <v>10.8910692811534</v>
       </c>
       <c r="D7">
-        <v>706</v>
+        <v>312</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>1992</v>
       </c>
       <c r="J7">
-        <v>23.8023347341202</v>
+        <v>22.2162568736526</v>
       </c>
       <c r="K7">
         <v>49</v>
@@ -4243,91 +4243,91 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="B8">
         <v>1993</v>
       </c>
       <c r="C8">
-        <v>18.0950975639669</v>
+        <v>16.7846787429652</v>
       </c>
       <c r="D8">
-        <v>1316</v>
+        <v>655</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="I8">
         <v>1993</v>
       </c>
       <c r="J8">
-        <v>31.705459221145</v>
+        <v>10.8910692811534</v>
       </c>
       <c r="K8">
-        <v>706</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="B9">
         <v>1993</v>
       </c>
       <c r="C9">
-        <v>17.974457820552</v>
+        <v>16.8973330080934</v>
       </c>
       <c r="D9">
-        <v>655</v>
+        <v>1316</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="I9">
         <v>1993</v>
       </c>
       <c r="J9">
-        <v>18.0950975639669</v>
+        <v>16.7846787429652</v>
       </c>
       <c r="K9">
-        <v>1316</v>
+        <v>655</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="B10">
         <v>1993</v>
       </c>
       <c r="C10">
-        <v>11.6630808615773</v>
+        <v>29.6067871831229</v>
       </c>
       <c r="D10">
-        <v>312</v>
+        <v>706</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="I10">
         <v>1993</v>
       </c>
       <c r="J10">
-        <v>17.974457820552</v>
+        <v>16.8973330080934</v>
       </c>
       <c r="K10">
-        <v>655</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="11">
@@ -4340,24 +4340,24 @@
         <v>1993</v>
       </c>
       <c r="C11">
-        <v>23.940440179247</v>
+        <v>22.3557562283954</v>
       </c>
       <c r="D11">
         <v>271</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="I11">
         <v>1993</v>
       </c>
       <c r="J11">
-        <v>11.6630808615773</v>
+        <v>29.6067871831229</v>
       </c>
       <c r="K11">
-        <v>312</v>
+        <v>706</v>
       </c>
     </row>
     <row r="12">
@@ -4370,7 +4370,7 @@
         <v>1994</v>
       </c>
       <c r="C12">
-        <v>30.6978148354907</v>
+        <v>28.6390954452377</v>
       </c>
       <c r="D12">
         <v>621</v>
@@ -4384,7 +4384,7 @@
         <v>1993</v>
       </c>
       <c r="J12">
-        <v>23.7324879603758</v>
+        <v>22.1615689420536</v>
       </c>
       <c r="K12">
         <v>215</v>
@@ -4400,7 +4400,7 @@
         <v>1994</v>
       </c>
       <c r="C13">
-        <v>11.9151115960081</v>
+        <v>11.1160361109553</v>
       </c>
       <c r="D13">
         <v>254</v>
@@ -4414,7 +4414,7 @@
         <v>1993</v>
       </c>
       <c r="J13">
-        <v>26.3487451891917</v>
+        <v>24.6046488687496</v>
       </c>
       <c r="K13">
         <v>56</v>
@@ -4430,7 +4430,7 @@
         <v>1994</v>
       </c>
       <c r="C14">
-        <v>23.0009836992135</v>
+        <v>21.4584448771434</v>
       </c>
       <c r="D14">
         <v>251</v>
@@ -4444,7 +4444,7 @@
         <v>1994</v>
       </c>
       <c r="J14">
-        <v>30.6978148354907</v>
+        <v>28.6390954452377</v>
       </c>
       <c r="K14">
         <v>621</v>
@@ -4460,7 +4460,7 @@
         <v>1994</v>
       </c>
       <c r="C15">
-        <v>18.2627803496898</v>
+        <v>17.038004572413</v>
       </c>
       <c r="D15">
         <v>543</v>
@@ -4474,7 +4474,7 @@
         <v>1994</v>
       </c>
       <c r="J15">
-        <v>11.9151115960081</v>
+        <v>11.1160361109553</v>
       </c>
       <c r="K15">
         <v>254</v>
@@ -4490,7 +4490,7 @@
         <v>1994</v>
       </c>
       <c r="C16">
-        <v>18.2675272494921</v>
+        <v>17.0424331259513</v>
       </c>
       <c r="D16">
         <v>1009</v>
@@ -4504,7 +4504,7 @@
         <v>1994</v>
       </c>
       <c r="J16">
-        <v>23.9530791680705</v>
+        <v>22.34668898024</v>
       </c>
       <c r="K16">
         <v>62</v>
@@ -4520,7 +4520,7 @@
         <v>1995</v>
       </c>
       <c r="C17">
-        <v>17.9688445197211</v>
+        <v>16.7715626665206</v>
       </c>
       <c r="D17">
         <v>535</v>
@@ -4534,7 +4534,7 @@
         <v>1994</v>
       </c>
       <c r="J17">
-        <v>18.2627803496898</v>
+        <v>17.038004572413</v>
       </c>
       <c r="K17">
         <v>543</v>
@@ -4550,7 +4550,7 @@
         <v>1995</v>
       </c>
       <c r="C18">
-        <v>11.3886000188192</v>
+        <v>10.6297663541989</v>
       </c>
       <c r="D18">
         <v>272</v>
@@ -4564,7 +4564,7 @@
         <v>1994</v>
       </c>
       <c r="J18">
-        <v>18.2675272494921</v>
+        <v>17.0424331259513</v>
       </c>
       <c r="K18">
         <v>1009</v>
@@ -4580,7 +4580,7 @@
         <v>1995</v>
       </c>
       <c r="C19">
-        <v>30.9679647572835</v>
+        <v>28.904538687023</v>
       </c>
       <c r="D19">
         <v>606</v>
@@ -4594,7 +4594,7 @@
         <v>1994</v>
       </c>
       <c r="J19">
-        <v>22.7113274894197</v>
+        <v>21.1882141821234</v>
       </c>
       <c r="K19">
         <v>189</v>
@@ -4610,7 +4610,7 @@
         <v>1995</v>
       </c>
       <c r="C20">
-        <v>24.0038916142781</v>
+        <v>22.4044886140225</v>
       </c>
       <c r="D20">
         <v>261</v>
@@ -4624,7 +4624,7 @@
         <v>1995</v>
       </c>
       <c r="J20">
-        <v>17.9688445197211</v>
+        <v>16.7715626665206</v>
       </c>
       <c r="K20">
         <v>535</v>
@@ -4640,7 +4640,7 @@
         <v>1995</v>
       </c>
       <c r="C21">
-        <v>18.5600222629971</v>
+        <v>17.3233496530195</v>
       </c>
       <c r="D21">
         <v>937</v>
@@ -4654,7 +4654,7 @@
         <v>1995</v>
       </c>
       <c r="J21">
-        <v>11.3886000188192</v>
+        <v>10.6297663541989</v>
       </c>
       <c r="K21">
         <v>272</v>
@@ -4670,7 +4670,7 @@
         <v>1996</v>
       </c>
       <c r="C22">
-        <v>31.2159073425062</v>
+        <v>29.1434553938331</v>
       </c>
       <c r="D22">
         <v>630</v>
@@ -4684,7 +4684,7 @@
         <v>1995</v>
       </c>
       <c r="J22">
-        <v>30.9679647572835</v>
+        <v>28.904538687023</v>
       </c>
       <c r="K22">
         <v>606</v>
@@ -4700,7 +4700,7 @@
         <v>1996</v>
       </c>
       <c r="C23">
-        <v>18.1617521702985</v>
+        <v>16.9559772343446</v>
       </c>
       <c r="D23">
         <v>917</v>
@@ -4714,7 +4714,7 @@
         <v>1995</v>
       </c>
       <c r="J23">
-        <v>22.8658151329888</v>
+        <v>21.3422432924445</v>
       </c>
       <c r="K23">
         <v>50</v>
@@ -4730,7 +4730,7 @@
         <v>1996</v>
       </c>
       <c r="C24">
-        <v>19.7197185016814</v>
+        <v>18.4105087905017</v>
       </c>
       <c r="D24">
         <v>483</v>
@@ -4744,7 +4744,7 @@
         <v>1995</v>
       </c>
       <c r="J24">
-        <v>18.5600222629971</v>
+        <v>17.3233496530195</v>
       </c>
       <c r="K24">
         <v>937</v>
@@ -4760,7 +4760,7 @@
         <v>1996</v>
       </c>
       <c r="C25">
-        <v>11.9657359185157</v>
+        <v>11.1713200314635</v>
       </c>
       <c r="D25">
         <v>268</v>
@@ -4774,7 +4774,7 @@
         <v>1995</v>
       </c>
       <c r="J25">
-        <v>24.3472676595052</v>
+        <v>22.7249851742987</v>
       </c>
       <c r="K25">
         <v>211</v>
@@ -4790,7 +4790,7 @@
         <v>1996</v>
       </c>
       <c r="C26">
-        <v>22.7528605502405</v>
+        <v>21.2422778313771</v>
       </c>
       <c r="D26">
         <v>281</v>
@@ -4804,7 +4804,7 @@
         <v>1996</v>
       </c>
       <c r="J26">
-        <v>31.2159073425062</v>
+        <v>29.1434553938331</v>
       </c>
       <c r="K26">
         <v>630</v>
@@ -4820,7 +4820,7 @@
         <v>1997</v>
       </c>
       <c r="C27">
-        <v>33.0127796358981</v>
+        <v>30.8273319387686</v>
       </c>
       <c r="D27">
         <v>633</v>
@@ -4834,7 +4834,7 @@
         <v>1996</v>
       </c>
       <c r="J27">
-        <v>18.1617521702985</v>
+        <v>16.9559772343446</v>
       </c>
       <c r="K27">
         <v>917</v>
@@ -4850,7 +4850,7 @@
         <v>1997</v>
       </c>
       <c r="C28">
-        <v>19.5606519145481</v>
+        <v>18.2657357592748</v>
       </c>
       <c r="D28">
         <v>472</v>
@@ -4864,7 +4864,7 @@
         <v>1996</v>
       </c>
       <c r="J28">
-        <v>19.7197185016814</v>
+        <v>18.4105087905017</v>
       </c>
       <c r="K28">
         <v>483</v>
@@ -4880,7 +4880,7 @@
         <v>1997</v>
       </c>
       <c r="C29">
-        <v>18.765819600073</v>
+        <v>17.5235213845924</v>
       </c>
       <c r="D29">
         <v>879</v>
@@ -4894,7 +4894,7 @@
         <v>1996</v>
       </c>
       <c r="J29">
-        <v>11.9657359185157</v>
+        <v>11.1713200314635</v>
       </c>
       <c r="K29">
         <v>268</v>
@@ -4910,7 +4910,7 @@
         <v>1997</v>
       </c>
       <c r="C30">
-        <v>23.911673186189</v>
+        <v>22.3287192006226</v>
       </c>
       <c r="D30">
         <v>285</v>
@@ -4924,7 +4924,7 @@
         <v>1996</v>
       </c>
       <c r="J30">
-        <v>23.1418067283961</v>
+        <v>21.6054015256303</v>
       </c>
       <c r="K30">
         <v>231</v>
@@ -4940,7 +4940,7 @@
         <v>1997</v>
       </c>
       <c r="C31">
-        <v>11.8133474800546</v>
+        <v>11.0313032738284</v>
       </c>
       <c r="D31">
         <v>248</v>
@@ -4954,7 +4954,7 @@
         <v>1996</v>
       </c>
       <c r="J31">
-        <v>21.8221305397166</v>
+        <v>20.3733398169285</v>
       </c>
       <c r="K31">
         <v>50</v>
@@ -4963,17 +4963,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="B32">
         <v>1998</v>
       </c>
       <c r="C32">
-        <v>19.3699780993637</v>
+        <v>18.3051395114559</v>
       </c>
       <c r="D32">
-        <v>470</v>
+        <v>875</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>1997</v>
       </c>
       <c r="J32">
-        <v>33.0127796358981</v>
+        <v>30.8273319387686</v>
       </c>
       <c r="K32">
         <v>633</v>
@@ -4993,17 +4993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="B33">
         <v>1998</v>
       </c>
       <c r="C33">
-        <v>32.7553152998156</v>
+        <v>11.8667826637916</v>
       </c>
       <c r="D33">
-        <v>626</v>
+        <v>264</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -5014,7 +5014,7 @@
         <v>1997</v>
       </c>
       <c r="J33">
-        <v>19.5606519145481</v>
+        <v>18.2657357592748</v>
       </c>
       <c r="K33">
         <v>472</v>
@@ -5023,17 +5023,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="B34">
         <v>1998</v>
       </c>
       <c r="C34">
-        <v>12.7090824168661</v>
+        <v>30.5844430775771</v>
       </c>
       <c r="D34">
-        <v>264</v>
+        <v>626</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -5044,7 +5044,7 @@
         <v>1997</v>
       </c>
       <c r="J34">
-        <v>18.765819600073</v>
+        <v>17.5235213845924</v>
       </c>
       <c r="K34">
         <v>879</v>
@@ -5053,17 +5053,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="B35">
         <v>1998</v>
       </c>
       <c r="C35">
-        <v>19.6044314027231</v>
+        <v>18.0862246988427</v>
       </c>
       <c r="D35">
-        <v>875</v>
+        <v>470</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -5074,7 +5074,7 @@
         <v>1997</v>
       </c>
       <c r="J35">
-        <v>23.786045860436</v>
+        <v>22.2114084102475</v>
       </c>
       <c r="K35">
         <v>237</v>
@@ -5090,7 +5090,7 @@
         <v>1998</v>
       </c>
       <c r="C36">
-        <v>23.3306265116535</v>
+        <v>21.7843794809661</v>
       </c>
       <c r="D36">
         <v>281</v>
@@ -5104,7 +5104,7 @@
         <v>1997</v>
       </c>
       <c r="J36">
-        <v>11.8133474800546</v>
+        <v>11.0313032738284</v>
       </c>
       <c r="K36">
         <v>248</v>
@@ -5120,7 +5120,7 @@
         <v>1999</v>
       </c>
       <c r="C37">
-        <v>19.8749998121551</v>
+        <v>18.5613953620957</v>
       </c>
       <c r="D37">
         <v>888</v>
@@ -5134,7 +5134,7 @@
         <v>1997</v>
       </c>
       <c r="J37">
-        <v>25.4348173707219</v>
+        <v>23.7510311623861</v>
       </c>
       <c r="K37">
         <v>48</v>
@@ -5150,24 +5150,24 @@
         <v>1999</v>
       </c>
       <c r="C38">
-        <v>34.2644208850283</v>
+        <v>31.999772020692</v>
       </c>
       <c r="D38">
         <v>602</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="I38">
         <v>1998</v>
       </c>
       <c r="J38">
-        <v>19.3699780993637</v>
+        <v>18.3051395114559</v>
       </c>
       <c r="K38">
-        <v>470</v>
+        <v>875</v>
       </c>
     </row>
     <row r="39">
@@ -5180,24 +5180,24 @@
         <v>1999</v>
       </c>
       <c r="C39">
-        <v>13.3825757648006</v>
+        <v>12.4980770858548</v>
       </c>
       <c r="D39">
         <v>277</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="I39">
         <v>1998</v>
       </c>
       <c r="J39">
-        <v>32.7553152998156</v>
+        <v>11.8667826637916</v>
       </c>
       <c r="K39">
-        <v>626</v>
+        <v>264</v>
       </c>
     </row>
     <row r="40">
@@ -5210,24 +5210,24 @@
         <v>1999</v>
       </c>
       <c r="C40">
-        <v>23.7099038470875</v>
+        <v>22.1428379100621</v>
       </c>
       <c r="D40">
         <v>263</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="I40">
         <v>1998</v>
       </c>
       <c r="J40">
-        <v>12.7090824168661</v>
+        <v>30.5844430775771</v>
       </c>
       <c r="K40">
-        <v>264</v>
+        <v>626</v>
       </c>
     </row>
     <row r="41">
@@ -5240,40 +5240,40 @@
         <v>1999</v>
       </c>
       <c r="C41">
-        <v>19.1712122252493</v>
+        <v>17.904123423733</v>
       </c>
       <c r="D41">
         <v>432</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="I41">
         <v>1998</v>
       </c>
       <c r="J41">
-        <v>19.6044314027231</v>
+        <v>18.0862246988427</v>
       </c>
       <c r="K41">
-        <v>875</v>
+        <v>470</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="B42">
         <v>2000</v>
       </c>
       <c r="C42">
-        <v>19.7843762180593</v>
+        <v>32.1346218536976</v>
       </c>
       <c r="D42">
-        <v>865</v>
+        <v>606</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -5284,7 +5284,7 @@
         <v>1998</v>
       </c>
       <c r="J42">
-        <v>22.9688054602282</v>
+        <v>21.4465382710648</v>
       </c>
       <c r="K42">
         <v>238</v>
@@ -5293,17 +5293,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="B43">
         <v>2000</v>
       </c>
       <c r="C43">
-        <v>13.7412871077509</v>
+        <v>19.2076332074334</v>
       </c>
       <c r="D43">
-        <v>289</v>
+        <v>457</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>1998</v>
       </c>
       <c r="J43">
-        <v>26.5928988592282</v>
+        <v>24.8304433641769</v>
       </c>
       <c r="K43">
         <v>43</v>
@@ -5323,17 +5323,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="B44">
         <v>2000</v>
       </c>
       <c r="C44">
-        <v>20.5768029921126</v>
+        <v>18.4679340993844</v>
       </c>
       <c r="D44">
-        <v>457</v>
+        <v>865</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -5344,7 +5344,7 @@
         <v>1999</v>
       </c>
       <c r="J44">
-        <v>19.8749998121551</v>
+        <v>18.5613953620957</v>
       </c>
       <c r="K44">
         <v>888</v>
@@ -5353,17 +5353,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>Associate degree-all</t>
         </is>
       </c>
       <c r="B45">
         <v>2000</v>
       </c>
       <c r="C45">
-        <v>34.4252608308698</v>
+        <v>22.7692278789445</v>
       </c>
       <c r="D45">
-        <v>606</v>
+        <v>272</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5374,7 +5374,7 @@
         <v>1999</v>
       </c>
       <c r="J45">
-        <v>34.2644208850283</v>
+        <v>31.999772020692</v>
       </c>
       <c r="K45">
         <v>602</v>
@@ -5383,17 +5383,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate degree-all</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="B46">
         <v>2000</v>
       </c>
       <c r="C46">
-        <v>24.3922773455629</v>
+        <v>12.8269490000407</v>
       </c>
       <c r="D46">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5404,7 +5404,7 @@
         <v>1999</v>
       </c>
       <c r="J46">
-        <v>13.3825757648006</v>
+        <v>12.4980770858548</v>
       </c>
       <c r="K46">
         <v>277</v>
@@ -5413,17 +5413,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="B47">
         <v>2001</v>
       </c>
       <c r="C47">
-        <v>13.6865806102202</v>
+        <v>19.1082779378333</v>
       </c>
       <c r="D47">
-        <v>360</v>
+        <v>616</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -5434,7 +5434,7 @@
         <v>1999</v>
       </c>
       <c r="J47">
-        <v>24.0172470699657</v>
+        <v>22.4298678031751</v>
       </c>
       <c r="K47">
         <v>206</v>
@@ -5443,17 +5443,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="B48">
         <v>2001</v>
       </c>
       <c r="C48">
-        <v>35.2929991522706</v>
+        <v>19.1354135831136</v>
       </c>
       <c r="D48">
-        <v>790</v>
+        <v>1094</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -5464,7 +5464,7 @@
         <v>1999</v>
       </c>
       <c r="J48">
-        <v>19.1712122252493</v>
+        <v>17.904123423733</v>
       </c>
       <c r="K48">
         <v>432</v>
@@ -5473,17 +5473,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="B49">
         <v>2001</v>
       </c>
       <c r="C49">
-        <v>20.3805297569537</v>
+        <v>33.1368292885887</v>
       </c>
       <c r="D49">
-        <v>1094</v>
+        <v>790</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>1999</v>
       </c>
       <c r="J49">
-        <v>23.0780303839481</v>
+        <v>21.5527270532573</v>
       </c>
       <c r="K49">
         <v>57</v>
@@ -5503,31 +5503,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="B50">
         <v>2001</v>
       </c>
       <c r="C50">
-        <v>20.3516284309537</v>
+        <v>12.8504206533606</v>
       </c>
       <c r="D50">
-        <v>616</v>
+        <v>360</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="I50">
         <v>2000</v>
       </c>
       <c r="J50">
-        <v>19.7843762180593</v>
+        <v>32.1346218536976</v>
       </c>
       <c r="K50">
-        <v>865</v>
+        <v>606</v>
       </c>
     </row>
     <row r="51">
@@ -5540,130 +5540,130 @@
         <v>2001</v>
       </c>
       <c r="C51">
-        <v>24.343179273844</v>
+        <v>22.8559713063373</v>
       </c>
       <c r="D51">
         <v>433</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="I51">
         <v>2000</v>
       </c>
       <c r="J51">
-        <v>13.7412871077509</v>
+        <v>19.2076332074334</v>
       </c>
       <c r="K51">
-        <v>289</v>
+        <v>457</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="B52">
         <v>2002</v>
       </c>
       <c r="C52">
-        <v>35.092319863777</v>
+        <v>19.7983635607633</v>
       </c>
       <c r="D52">
-        <v>991</v>
+        <v>1326</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="I52">
         <v>2000</v>
       </c>
       <c r="J52">
-        <v>20.5768029921126</v>
+        <v>18.4679340993844</v>
       </c>
       <c r="K52">
-        <v>457</v>
+        <v>865</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="B53">
         <v>2002</v>
       </c>
       <c r="C53">
-        <v>21.0176269098879</v>
+        <v>19.6647103702661</v>
       </c>
       <c r="D53">
-        <v>1326</v>
+        <v>733</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>Associate degree-academic program</t>
         </is>
       </c>
       <c r="I53">
         <v>2000</v>
       </c>
       <c r="J53">
-        <v>34.4252608308698</v>
+        <v>23.6158742621926</v>
       </c>
       <c r="K53">
-        <v>606</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="B54">
         <v>2002</v>
       </c>
       <c r="C54">
-        <v>14.2263457592551</v>
+        <v>33.0565629427361</v>
       </c>
       <c r="D54">
-        <v>402</v>
+        <v>991</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Associate degree-academic program</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="I54">
         <v>2000</v>
       </c>
       <c r="J54">
-        <v>25.2992748732614</v>
+        <v>12.8269490000407</v>
       </c>
       <c r="K54">
-        <v>70</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="B55">
         <v>2002</v>
       </c>
       <c r="C55">
-        <v>20.8757428150452</v>
+        <v>13.4010545857747</v>
       </c>
       <c r="D55">
-        <v>733</v>
+        <v>402</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>2000</v>
       </c>
       <c r="J55">
-        <v>24.002889064751</v>
+        <v>22.4057492921118</v>
       </c>
       <c r="K55">
         <v>202</v>
@@ -5690,24 +5690,24 @@
         <v>2002</v>
       </c>
       <c r="C56">
-        <v>24.7389010229826</v>
+        <v>23.3037611071269</v>
       </c>
       <c r="D56">
         <v>502</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="I56">
         <v>2001</v>
       </c>
       <c r="J56">
-        <v>13.6865806102202</v>
+        <v>19.1082779378333</v>
       </c>
       <c r="K56">
-        <v>360</v>
+        <v>616</v>
       </c>
     </row>
     <row r="57">
@@ -5720,24 +5720,24 @@
         <v>2003</v>
       </c>
       <c r="C57">
-        <v>20.9451818148059</v>
+        <v>19.767059185757</v>
       </c>
       <c r="D57">
         <v>747</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="I57">
         <v>2001</v>
       </c>
       <c r="J57">
-        <v>35.2929991522706</v>
+        <v>19.1354135831136</v>
       </c>
       <c r="K57">
-        <v>790</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="58">
@@ -5750,24 +5750,24 @@
         <v>2003</v>
       </c>
       <c r="C58">
-        <v>13.5321534731549</v>
+        <v>12.7709981693983</v>
       </c>
       <c r="D58">
         <v>389</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="I58">
         <v>2001</v>
       </c>
       <c r="J58">
-        <v>20.3805297569537</v>
+        <v>33.1368292885887</v>
       </c>
       <c r="K58">
-        <v>1094</v>
+        <v>790</v>
       </c>
     </row>
     <row r="59">
@@ -5780,24 +5780,24 @@
         <v>2003</v>
       </c>
       <c r="C59">
-        <v>25.2328205267706</v>
+        <v>23.8135271962012</v>
       </c>
       <c r="D59">
         <v>503</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="I59">
         <v>2001</v>
       </c>
       <c r="J59">
-        <v>20.3516284309537</v>
+        <v>12.8504206533606</v>
       </c>
       <c r="K59">
-        <v>616</v>
+        <v>360</v>
       </c>
     </row>
     <row r="60">
@@ -5810,7 +5810,7 @@
         <v>2003</v>
       </c>
       <c r="C60">
-        <v>35.2771822340494</v>
+        <v>33.2929145849791</v>
       </c>
       <c r="D60">
         <v>1025</v>
@@ -5824,7 +5824,7 @@
         <v>2001</v>
       </c>
       <c r="J60">
-        <v>23.9319961916542</v>
+        <v>22.4699088030602</v>
       </c>
       <c r="K60">
         <v>339</v>
@@ -5840,7 +5840,7 @@
         <v>2003</v>
       </c>
       <c r="C61">
-        <v>20.7035890007302</v>
+        <v>19.5390554617066</v>
       </c>
       <c r="D61">
         <v>1364</v>
@@ -5854,7 +5854,7 @@
         <v>2001</v>
       </c>
       <c r="J61">
-        <v>25.7994784489934</v>
+        <v>24.2233001907948</v>
       </c>
       <c r="K61">
         <v>94</v>
@@ -5870,24 +5870,24 @@
         <v>2004</v>
       </c>
       <c r="C62">
-        <v>20.6726405078323</v>
+        <v>19.5410630943333</v>
       </c>
       <c r="D62">
         <v>1333</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="I62">
         <v>2002</v>
       </c>
       <c r="J62">
-        <v>35.092319863777</v>
+        <v>19.7983635607633</v>
       </c>
       <c r="K62">
-        <v>991</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="63">
@@ -5900,24 +5900,24 @@
         <v>2004</v>
       </c>
       <c r="C63">
-        <v>13.2572202166065</v>
+        <v>12.5315475113122</v>
       </c>
       <c r="D63">
         <v>375</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="I63">
         <v>2002</v>
       </c>
       <c r="J63">
-        <v>21.0176269098879</v>
+        <v>19.6647103702661</v>
       </c>
       <c r="K63">
-        <v>1326</v>
+        <v>733</v>
       </c>
     </row>
     <row r="64">
@@ -5930,24 +5930,24 @@
         <v>2004</v>
       </c>
       <c r="C64">
-        <v>19.0686912949765</v>
+        <v>18.0249107306985</v>
       </c>
       <c r="D64">
         <v>702</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="I64">
         <v>2002</v>
       </c>
       <c r="J64">
-        <v>14.2263457592551</v>
+        <v>33.0565629427361</v>
       </c>
       <c r="K64">
-        <v>402</v>
+        <v>991</v>
       </c>
     </row>
     <row r="65">
@@ -5960,24 +5960,24 @@
         <v>2004</v>
       </c>
       <c r="C65">
-        <v>34.381424322025</v>
+        <v>32.499456549597</v>
       </c>
       <c r="D65">
         <v>989</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="I65">
         <v>2002</v>
       </c>
       <c r="J65">
-        <v>20.8757428150452</v>
+        <v>13.4010545857747</v>
       </c>
       <c r="K65">
-        <v>733</v>
+        <v>402</v>
       </c>
     </row>
     <row r="66">
@@ -5990,7 +5990,7 @@
         <v>2004</v>
       </c>
       <c r="C66">
-        <v>24.7969791226439</v>
+        <v>23.4396439777909</v>
       </c>
       <c r="D66">
         <v>472</v>
@@ -6004,7 +6004,7 @@
         <v>2002</v>
       </c>
       <c r="J66">
-        <v>24.7822215486603</v>
+        <v>23.3445685456016</v>
       </c>
       <c r="K66">
         <v>382</v>
@@ -6020,7 +6020,7 @@
         <v>2005</v>
       </c>
       <c r="C67">
-        <v>35.6344277832095</v>
+        <v>33.8467584287564</v>
       </c>
       <c r="D67">
         <v>901</v>
@@ -6034,7 +6034,7 @@
         <v>2002</v>
       </c>
       <c r="J67">
-        <v>24.5115722283167</v>
+        <v>23.0896199891061</v>
       </c>
       <c r="K67">
         <v>120</v>
@@ -6050,7 +6050,7 @@
         <v>2005</v>
       </c>
       <c r="C68">
-        <v>25.9042958573922</v>
+        <v>24.6047572164275</v>
       </c>
       <c r="D68">
         <v>475</v>
@@ -6064,7 +6064,7 @@
         <v>2003</v>
       </c>
       <c r="J68">
-        <v>20.9451818148059</v>
+        <v>19.767059185757</v>
       </c>
       <c r="K68">
         <v>747</v>
@@ -6080,7 +6080,7 @@
         <v>2005</v>
       </c>
       <c r="C69">
-        <v>20.7508188169762</v>
+        <v>19.7098142271285</v>
       </c>
       <c r="D69">
         <v>1216</v>
@@ -6094,7 +6094,7 @@
         <v>2003</v>
       </c>
       <c r="J69">
-        <v>13.5321534731549</v>
+        <v>12.7709981693983</v>
       </c>
       <c r="K69">
         <v>389</v>
@@ -6110,7 +6110,7 @@
         <v>2005</v>
       </c>
       <c r="C70">
-        <v>19.8432202062793</v>
+        <v>18.8477470399291</v>
       </c>
       <c r="D70">
         <v>659</v>
@@ -6124,7 +6124,7 @@
         <v>2003</v>
       </c>
       <c r="J70">
-        <v>25.7140741903222</v>
+        <v>24.2677113486663</v>
       </c>
       <c r="K70">
         <v>124</v>
@@ -6140,7 +6140,7 @@
         <v>2005</v>
       </c>
       <c r="C71">
-        <v>13.0578737019161</v>
+        <v>12.4028004454224</v>
       </c>
       <c r="D71">
         <v>349</v>
@@ -6154,7 +6154,7 @@
         <v>2003</v>
       </c>
       <c r="J71">
-        <v>35.2771822340494</v>
+        <v>33.2929145849791</v>
       </c>
       <c r="K71">
         <v>1025</v>
@@ -6170,7 +6170,7 @@
         <v>2006</v>
       </c>
       <c r="C72">
-        <v>33.83127933021</v>
+        <v>32.241751565004</v>
       </c>
       <c r="D72">
         <v>922</v>
@@ -6184,7 +6184,7 @@
         <v>2003</v>
       </c>
       <c r="J72">
-        <v>20.7035890007302</v>
+        <v>19.5390554617066</v>
       </c>
       <c r="K72">
         <v>1364</v>
@@ -6200,7 +6200,7 @@
         <v>2006</v>
       </c>
       <c r="C73">
-        <v>23.9700578038742</v>
+        <v>22.843849361061</v>
       </c>
       <c r="D73">
         <v>495</v>
@@ -6214,7 +6214,7 @@
         <v>2003</v>
       </c>
       <c r="J73">
-        <v>25.0401161475213</v>
+        <v>23.6316620348646</v>
       </c>
       <c r="K73">
         <v>379</v>
@@ -6230,7 +6230,7 @@
         <v>2006</v>
       </c>
       <c r="C74">
-        <v>19.4128001925508</v>
+        <v>18.5007097981771</v>
       </c>
       <c r="D74">
         <v>606</v>
@@ -6244,7 +6244,7 @@
         <v>2004</v>
       </c>
       <c r="J74">
-        <v>20.6726405078323</v>
+        <v>19.5410630943333</v>
       </c>
       <c r="K74">
         <v>1333</v>
@@ -6260,7 +6260,7 @@
         <v>2006</v>
       </c>
       <c r="C75">
-        <v>19.8752686249311</v>
+        <v>18.9414496282594</v>
       </c>
       <c r="D75">
         <v>1231</v>
@@ -6274,7 +6274,7 @@
         <v>2004</v>
       </c>
       <c r="J75">
-        <v>13.2572202166065</v>
+        <v>12.5315475113122</v>
       </c>
       <c r="K75">
         <v>375</v>
@@ -6290,7 +6290,7 @@
         <v>2006</v>
       </c>
       <c r="C76">
-        <v>12.5865065837818</v>
+        <v>11.9951425538674</v>
       </c>
       <c r="D76">
         <v>293</v>
@@ -6304,7 +6304,7 @@
         <v>2004</v>
       </c>
       <c r="J76">
-        <v>19.0686912949765</v>
+        <v>18.0249107306985</v>
       </c>
       <c r="K76">
         <v>702</v>
@@ -6320,7 +6320,7 @@
         <v>2007</v>
       </c>
       <c r="C77">
-        <v>34.0555607821744</v>
+        <v>32.543027537028</v>
       </c>
       <c r="D77">
         <v>987</v>
@@ -6334,7 +6334,7 @@
         <v>2004</v>
       </c>
       <c r="J77">
-        <v>34.381424322025</v>
+        <v>32.499456549597</v>
       </c>
       <c r="K77">
         <v>989</v>
@@ -6350,7 +6350,7 @@
         <v>2007</v>
       </c>
       <c r="C78">
-        <v>20.3596120412238</v>
+        <v>19.4553664683024</v>
       </c>
       <c r="D78">
         <v>1208</v>
@@ -6364,7 +6364,7 @@
         <v>2004</v>
       </c>
       <c r="J78">
-        <v>24.6041184143039</v>
+        <v>23.2573400641394</v>
       </c>
       <c r="K78">
         <v>355</v>
@@ -6380,7 +6380,7 @@
         <v>2007</v>
       </c>
       <c r="C79">
-        <v>12.1707003950014</v>
+        <v>11.6301546356201</v>
       </c>
       <c r="D79">
         <v>299</v>
@@ -6394,7 +6394,7 @@
         <v>2004</v>
       </c>
       <c r="J79">
-        <v>25.3036811566955</v>
+        <v>23.9186101946939</v>
       </c>
       <c r="K79">
         <v>117</v>
@@ -6410,7 +6410,7 @@
         <v>2007</v>
       </c>
       <c r="C80">
-        <v>19.2367148407193</v>
+        <v>18.3823412801107</v>
       </c>
       <c r="D80">
         <v>613</v>
@@ -6424,7 +6424,7 @@
         <v>2005</v>
       </c>
       <c r="J80">
-        <v>35.6344277832095</v>
+        <v>33.8467584287564</v>
       </c>
       <c r="K80">
         <v>901</v>
@@ -6440,7 +6440,7 @@
         <v>2007</v>
       </c>
       <c r="C81">
-        <v>25.1277404629608</v>
+        <v>24.0117246948242</v>
       </c>
       <c r="D81">
         <v>477</v>
@@ -6454,7 +6454,7 @@
         <v>2005</v>
       </c>
       <c r="J81">
-        <v>25.2615759592482</v>
+        <v>23.9942805935902</v>
       </c>
       <c r="K81">
         <v>112</v>
@@ -6470,7 +6470,7 @@
         <v>2008</v>
       </c>
       <c r="C82">
-        <v>19.5433605147586</v>
+        <v>18.7079298322377</v>
       </c>
       <c r="D82">
         <v>1112</v>
@@ -6484,7 +6484,7 @@
         <v>2005</v>
       </c>
       <c r="J82">
-        <v>20.7508188169762</v>
+        <v>19.7098142271285</v>
       </c>
       <c r="K82">
         <v>1216</v>
@@ -6500,7 +6500,7 @@
         <v>2008</v>
       </c>
       <c r="C83">
-        <v>11.7367795738259</v>
+        <v>11.23506106116</v>
       </c>
       <c r="D83">
         <v>286</v>
@@ -6514,7 +6514,7 @@
         <v>2005</v>
       </c>
       <c r="J83">
-        <v>19.8432202062793</v>
+        <v>18.8477470399291</v>
       </c>
       <c r="K83">
         <v>659</v>
@@ -6530,7 +6530,7 @@
         <v>2008</v>
       </c>
       <c r="C84">
-        <v>33.406044478051</v>
+        <v>31.978018089368</v>
       </c>
       <c r="D84">
         <v>1048</v>
@@ -6544,7 +6544,7 @@
         <v>2005</v>
       </c>
       <c r="J84">
-        <v>13.0578737019161</v>
+        <v>12.4028004454224</v>
       </c>
       <c r="K84">
         <v>349</v>
@@ -6560,7 +6560,7 @@
         <v>2008</v>
       </c>
       <c r="C85">
-        <v>24.4414702905289</v>
+        <v>23.3966574400874</v>
       </c>
       <c r="D85">
         <v>505</v>
@@ -6574,7 +6574,7 @@
         <v>2005</v>
       </c>
       <c r="J85">
-        <v>26.1589611725434</v>
+        <v>24.8466467580401</v>
       </c>
       <c r="K85">
         <v>363</v>
@@ -6590,7 +6590,7 @@
         <v>2008</v>
       </c>
       <c r="C86">
-        <v>18.4062697798335</v>
+        <v>17.6194469346418</v>
       </c>
       <c r="D86">
         <v>656</v>
@@ -6604,7 +6604,7 @@
         <v>2006</v>
       </c>
       <c r="J86">
-        <v>33.83127933021</v>
+        <v>32.241751565004</v>
       </c>
       <c r="K86">
         <v>922</v>
@@ -6620,7 +6620,7 @@
         <v>2009</v>
       </c>
       <c r="C87">
-        <v>19.931834534232</v>
+        <v>19.090067026848</v>
       </c>
       <c r="D87">
         <v>1036</v>
@@ -6634,7 +6634,7 @@
         <v>2006</v>
       </c>
       <c r="J87">
-        <v>25.7164845129586</v>
+        <v>24.5082220125117</v>
       </c>
       <c r="K87">
         <v>127</v>
@@ -6650,7 +6650,7 @@
         <v>2009</v>
       </c>
       <c r="C88">
-        <v>33.8804654799304</v>
+        <v>32.449615001663</v>
       </c>
       <c r="D88">
         <v>1078</v>
@@ -6664,7 +6664,7 @@
         <v>2006</v>
       </c>
       <c r="J88">
-        <v>19.4128001925508</v>
+        <v>18.5007097981771</v>
       </c>
       <c r="K88">
         <v>606</v>
@@ -6680,7 +6680,7 @@
         <v>2009</v>
       </c>
       <c r="C89">
-        <v>25.152945871538</v>
+        <v>24.0906787473911</v>
       </c>
       <c r="D89">
         <v>455</v>
@@ -6694,7 +6694,7 @@
         <v>2006</v>
       </c>
       <c r="J89">
-        <v>19.8752686249311</v>
+        <v>18.9414496282594</v>
       </c>
       <c r="K89">
         <v>1231</v>
@@ -6710,7 +6710,7 @@
         <v>2009</v>
       </c>
       <c r="C90">
-        <v>18.78695862991</v>
+        <v>17.99354188194</v>
       </c>
       <c r="D90">
         <v>706</v>
@@ -6724,7 +6724,7 @@
         <v>2006</v>
       </c>
       <c r="J90">
-        <v>12.5865065837818</v>
+        <v>11.9951425538674</v>
       </c>
       <c r="K90">
         <v>293</v>
@@ -6740,7 +6740,7 @@
         <v>2009</v>
       </c>
       <c r="C91">
-        <v>11.8889100596304</v>
+        <v>11.3868138692762</v>
       </c>
       <c r="D91">
         <v>232</v>
@@ -6754,7 +6754,7 @@
         <v>2006</v>
       </c>
       <c r="J91">
-        <v>23.3782775231943</v>
+        <v>22.2798732664972</v>
       </c>
       <c r="K91">
         <v>368</v>
@@ -6770,7 +6770,7 @@
         <v>2010</v>
       </c>
       <c r="C92">
-        <v>13.2613526410502</v>
+        <v>12.7324326426512</v>
       </c>
       <c r="D92">
         <v>248</v>
@@ -6784,7 +6784,7 @@
         <v>2007</v>
       </c>
       <c r="J92">
-        <v>34.0555607821744</v>
+        <v>32.543027537028</v>
       </c>
       <c r="K92">
         <v>987</v>
@@ -6800,7 +6800,7 @@
         <v>2010</v>
       </c>
       <c r="C93">
-        <v>20.2143771459044</v>
+        <v>19.4081405109964</v>
       </c>
       <c r="D93">
         <v>1015</v>
@@ -6814,7 +6814,7 @@
         <v>2007</v>
       </c>
       <c r="J93">
-        <v>20.3596120412238</v>
+        <v>19.4553664683024</v>
       </c>
       <c r="K93">
         <v>1208</v>
@@ -6830,7 +6830,7 @@
         <v>2010</v>
       </c>
       <c r="C94">
-        <v>32.1721994437002</v>
+        <v>30.8890332283943</v>
       </c>
       <c r="D94">
         <v>1141</v>
@@ -6844,7 +6844,7 @@
         <v>2007</v>
       </c>
       <c r="J94">
-        <v>12.1707003950014</v>
+        <v>11.6301546356201</v>
       </c>
       <c r="K94">
         <v>299</v>
@@ -6860,7 +6860,7 @@
         <v>2010</v>
       </c>
       <c r="C95">
-        <v>19.2340993135702</v>
+        <v>18.4669603909049</v>
       </c>
       <c r="D95">
         <v>667</v>
@@ -6874,7 +6874,7 @@
         <v>2007</v>
       </c>
       <c r="J95">
-        <v>19.2367148407193</v>
+        <v>18.3823412801107</v>
       </c>
       <c r="K95">
         <v>613</v>
@@ -6890,7 +6890,7 @@
         <v>2010</v>
       </c>
       <c r="C96">
-        <v>25.1228033057446</v>
+        <v>24.1207974437543</v>
       </c>
       <c r="D96">
         <v>452</v>
@@ -6904,7 +6904,7 @@
         <v>2007</v>
       </c>
       <c r="J96">
-        <v>26.0737570066744</v>
+        <v>24.9157251495361</v>
       </c>
       <c r="K96">
         <v>312</v>
@@ -6920,7 +6920,7 @@
         <v>2011</v>
       </c>
       <c r="C97">
-        <v>12.1146968841553</v>
+        <v>11.6410315780345</v>
       </c>
       <c r="D97">
         <v>250</v>
@@ -6934,7 +6934,7 @@
         <v>2007</v>
       </c>
       <c r="J97">
-        <v>23.7532456804757</v>
+        <v>22.698276302592</v>
       </c>
       <c r="K97">
         <v>165</v>
@@ -6950,7 +6950,7 @@
         <v>2011</v>
       </c>
       <c r="C98">
-        <v>19.262984829238</v>
+        <v>18.5098328772585</v>
       </c>
       <c r="D98">
         <v>1025</v>
@@ -6964,7 +6964,7 @@
         <v>2008</v>
       </c>
       <c r="J98">
-        <v>19.5433605147586</v>
+        <v>18.7079298322377</v>
       </c>
       <c r="K98">
         <v>1112</v>
@@ -6980,7 +6980,7 @@
         <v>2011</v>
       </c>
       <c r="C99">
-        <v>17.8721212762775</v>
+        <v>17.1733498685977</v>
       </c>
       <c r="D99">
         <v>682</v>
@@ -6994,7 +6994,7 @@
         <v>2008</v>
       </c>
       <c r="J99">
-        <v>11.7367795738259</v>
+        <v>11.23506106116</v>
       </c>
       <c r="K99">
         <v>286</v>
@@ -7010,7 +7010,7 @@
         <v>2011</v>
       </c>
       <c r="C100">
-        <v>32.4631895325401</v>
+        <v>31.1939306518083</v>
       </c>
       <c r="D100">
         <v>1127</v>
@@ -7024,7 +7024,7 @@
         <v>2008</v>
       </c>
       <c r="J100">
-        <v>33.406044478051</v>
+        <v>31.978018089368</v>
       </c>
       <c r="K100">
         <v>1048</v>
@@ -7040,7 +7040,7 @@
         <v>2011</v>
       </c>
       <c r="C101">
-        <v>24.4222421761715</v>
+        <v>23.46737149908</v>
       </c>
       <c r="D101">
         <v>474</v>
@@ -7054,7 +7054,7 @@
         <v>2008</v>
       </c>
       <c r="J101">
-        <v>24.0003589907351</v>
+        <v>22.9744025654195</v>
       </c>
       <c r="K101">
         <v>341</v>
@@ -7070,7 +7070,7 @@
         <v>2012</v>
       </c>
       <c r="C102">
-        <v>18.791585042166</v>
+        <v>18.085280002016</v>
       </c>
       <c r="D102">
         <v>950</v>
@@ -7084,7 +7084,7 @@
         <v>2008</v>
       </c>
       <c r="J102">
-        <v>18.4062697798335</v>
+        <v>17.6194469346418</v>
       </c>
       <c r="K102">
         <v>656</v>
@@ -7100,7 +7100,7 @@
         <v>2012</v>
       </c>
       <c r="C103">
-        <v>11.9077618633756</v>
+        <v>11.4601938587536</v>
       </c>
       <c r="D103">
         <v>239</v>
@@ -7114,7 +7114,7 @@
         <v>2008</v>
       </c>
       <c r="J103">
-        <v>24.8511522340201</v>
+        <v>23.7888264862747</v>
       </c>
       <c r="K103">
         <v>164</v>
@@ -7130,7 +7130,7 @@
         <v>2012</v>
       </c>
       <c r="C104">
-        <v>32.4595726813715</v>
+        <v>31.239539366751</v>
       </c>
       <c r="D104">
         <v>1121</v>
@@ -7144,7 +7144,7 @@
         <v>2009</v>
       </c>
       <c r="J104">
-        <v>19.931834534232</v>
+        <v>19.090067026848</v>
       </c>
       <c r="K104">
         <v>1036</v>
@@ -7160,7 +7160,7 @@
         <v>2012</v>
       </c>
       <c r="C105">
-        <v>16.835878613654</v>
+        <v>16.2030812262333</v>
       </c>
       <c r="D105">
         <v>684</v>
@@ -7174,7 +7174,7 @@
         <v>2009</v>
       </c>
       <c r="J105">
-        <v>33.8804654799304</v>
+        <v>32.449615001663</v>
       </c>
       <c r="K105">
         <v>1078</v>
@@ -7190,7 +7190,7 @@
         <v>2012</v>
       </c>
       <c r="C106">
-        <v>24.2646170893845</v>
+        <v>23.352601348877</v>
       </c>
       <c r="D106">
         <v>531</v>
@@ -7204,7 +7204,7 @@
         <v>2009</v>
       </c>
       <c r="J106">
-        <v>24.7427365588203</v>
+        <v>23.6977935234359</v>
       </c>
       <c r="K106">
         <v>305</v>
@@ -7220,7 +7220,7 @@
         <v>2013</v>
       </c>
       <c r="C107">
-        <v>12.40095024081</v>
+        <v>11.97041911188</v>
       </c>
       <c r="D107">
         <v>252</v>
@@ -7234,7 +7234,7 @@
         <v>2009</v>
       </c>
       <c r="J107">
-        <v>18.78695862991</v>
+        <v>17.99354188194</v>
       </c>
       <c r="K107">
         <v>706</v>
@@ -7250,7 +7250,7 @@
         <v>2013</v>
       </c>
       <c r="C108">
-        <v>18.1282834644206</v>
+        <v>17.4989131182825</v>
       </c>
       <c r="D108">
         <v>637</v>
@@ -7264,7 +7264,7 @@
         <v>2009</v>
       </c>
       <c r="J108">
-        <v>11.8889100596304</v>
+        <v>11.3868138692762</v>
       </c>
       <c r="K108">
         <v>232</v>
@@ -7280,7 +7280,7 @@
         <v>2013</v>
       </c>
       <c r="C109">
-        <v>23.7092102786951</v>
+        <v>22.8860835933114</v>
       </c>
       <c r="D109">
         <v>544</v>
@@ -7294,7 +7294,7 @@
         <v>2009</v>
       </c>
       <c r="J109">
-        <v>25.8005732265699</v>
+        <v>24.7109553001964</v>
       </c>
       <c r="K109">
         <v>150</v>
@@ -7310,7 +7310,7 @@
         <v>2013</v>
       </c>
       <c r="C110">
-        <v>18.56392870033</v>
+        <v>17.919433800703</v>
       </c>
       <c r="D110">
         <v>928</v>
@@ -7324,7 +7324,7 @@
         <v>2010</v>
       </c>
       <c r="J110">
-        <v>13.2613526410502</v>
+        <v>12.7324326426512</v>
       </c>
       <c r="K110">
         <v>248</v>
@@ -7340,7 +7340,7 @@
         <v>2013</v>
       </c>
       <c r="C111">
-        <v>32.5111281383805</v>
+        <v>31.3824200613056</v>
       </c>
       <c r="D111">
         <v>1134</v>
@@ -7354,7 +7354,7 @@
         <v>2010</v>
       </c>
       <c r="J111">
-        <v>20.2143771459044</v>
+        <v>19.4081405109964</v>
       </c>
       <c r="K111">
         <v>1015</v>
@@ -7370,7 +7370,7 @@
         <v>2014</v>
       </c>
       <c r="C112">
-        <v>19.5821728773559</v>
+        <v>18.9478971776083</v>
       </c>
       <c r="D112">
         <v>982</v>
@@ -7384,7 +7384,7 @@
         <v>2010</v>
       </c>
       <c r="J112">
-        <v>32.1721994437002</v>
+        <v>30.8890332283943</v>
       </c>
       <c r="K112">
         <v>1141</v>
@@ -7400,7 +7400,7 @@
         <v>2014</v>
       </c>
       <c r="C113">
-        <v>24.6222102467205</v>
+        <v>23.8246853892196</v>
       </c>
       <c r="D113">
         <v>527</v>
@@ -7414,7 +7414,7 @@
         <v>2010</v>
       </c>
       <c r="J113">
-        <v>19.2340993135702</v>
+        <v>18.4669603909049</v>
       </c>
       <c r="K113">
         <v>667</v>
@@ -7430,7 +7430,7 @@
         <v>2014</v>
       </c>
       <c r="C114">
-        <v>18.5907590145828</v>
+        <v>17.9885956715939</v>
       </c>
       <c r="D114">
         <v>584</v>
@@ -7444,7 +7444,7 @@
         <v>2010</v>
       </c>
       <c r="J114">
-        <v>25.1444963308481</v>
+        <v>24.1416252573584</v>
       </c>
       <c r="K114">
         <v>322</v>
@@ -7460,7 +7460,7 @@
         <v>2014</v>
       </c>
       <c r="C115">
-        <v>33.6251192117581</v>
+        <v>32.5359859398423</v>
       </c>
       <c r="D115">
         <v>1040</v>
@@ -7474,7 +7474,7 @@
         <v>2010</v>
       </c>
       <c r="J115">
-        <v>25.0611365296231</v>
+        <v>24.0615902049071</v>
       </c>
       <c r="K115">
         <v>130</v>
@@ -7490,7 +7490,7 @@
         <v>2014</v>
       </c>
       <c r="C116">
-        <v>12.3056656374203</v>
+        <v>11.9070793961528</v>
       </c>
       <c r="D116">
         <v>224</v>
@@ -7504,7 +7504,7 @@
         <v>2011</v>
       </c>
       <c r="J116">
-        <v>12.1146968841553</v>
+        <v>11.6410315780345</v>
       </c>
       <c r="K116">
         <v>250</v>
@@ -7520,7 +7520,7 @@
         <v>2015</v>
       </c>
       <c r="C117">
-        <v>11.9243468274476</v>
+        <v>11.5665583456425</v>
       </c>
       <c r="D117">
         <v>190</v>
@@ -7534,7 +7534,7 @@
         <v>2011</v>
       </c>
       <c r="J117">
-        <v>19.262984829238</v>
+        <v>18.5098328772585</v>
       </c>
       <c r="K117">
         <v>1025</v>
@@ -7550,7 +7550,7 @@
         <v>2015</v>
       </c>
       <c r="C118">
-        <v>18.3910343532688</v>
+        <v>17.8392137499856</v>
       </c>
       <c r="D118">
         <v>484</v>
@@ -7564,7 +7564,7 @@
         <v>2011</v>
       </c>
       <c r="J118">
-        <v>17.8721212762775</v>
+        <v>17.1733498685977</v>
       </c>
       <c r="K118">
         <v>682</v>
@@ -7580,7 +7580,7 @@
         <v>2015</v>
       </c>
       <c r="C119">
-        <v>32.8610284281229</v>
+        <v>31.8750375271548</v>
       </c>
       <c r="D119">
         <v>919</v>
@@ -7594,7 +7594,7 @@
         <v>2011</v>
       </c>
       <c r="J119">
-        <v>32.4631895325401</v>
+        <v>31.1939306518083</v>
       </c>
       <c r="K119">
         <v>1127</v>
@@ -7610,7 +7610,7 @@
         <v>2015</v>
       </c>
       <c r="C120">
-        <v>19.5431809914102</v>
+        <v>18.9567903775056</v>
       </c>
       <c r="D120">
         <v>762</v>
@@ -7624,7 +7624,7 @@
         <v>2011</v>
       </c>
       <c r="J120">
-        <v>25.2502452705846</v>
+        <v>24.2630009944724</v>
       </c>
       <c r="K120">
         <v>311</v>
@@ -7640,7 +7640,7 @@
         <v>2015</v>
       </c>
       <c r="C121">
-        <v>25.1069203129521</v>
+        <v>24.3535904214653</v>
       </c>
       <c r="D121">
         <v>395</v>
@@ -7654,7 +7654,7 @@
         <v>2011</v>
       </c>
       <c r="J121">
-        <v>23.3752167326031</v>
+        <v>22.4612830786981</v>
       </c>
       <c r="K121">
         <v>163</v>
@@ -7670,7 +7670,7 @@
         <v>2016</v>
       </c>
       <c r="C122">
-        <v>34.4173807540989</v>
+        <v>33.5189524213531</v>
       </c>
       <c r="D122">
         <v>825</v>
@@ -7684,7 +7684,7 @@
         <v>2012</v>
       </c>
       <c r="J122">
-        <v>18.791585042166</v>
+        <v>18.085280002016</v>
       </c>
       <c r="K122">
         <v>950</v>
@@ -7700,7 +7700,7 @@
         <v>2016</v>
       </c>
       <c r="C123">
-        <v>19.1165093121345</v>
+        <v>18.6174936051599</v>
       </c>
       <c r="D123">
         <v>514</v>
@@ -7714,7 +7714,7 @@
         <v>2012</v>
       </c>
       <c r="J123">
-        <v>11.9077618633756</v>
+        <v>11.4601938587536</v>
       </c>
       <c r="K123">
         <v>239</v>
@@ -7730,7 +7730,7 @@
         <v>2016</v>
       </c>
       <c r="C124">
-        <v>12.4130385127468</v>
+        <v>12.0890096281842</v>
       </c>
       <c r="D124">
         <v>172</v>
@@ -7744,7 +7744,7 @@
         <v>2012</v>
       </c>
       <c r="J124">
-        <v>32.4595726813715</v>
+        <v>31.239539366751</v>
       </c>
       <c r="K124">
         <v>1121</v>
@@ -7760,7 +7760,7 @@
         <v>2016</v>
       </c>
       <c r="C125">
-        <v>20.2508929851644</v>
+        <v>19.7222654248261</v>
       </c>
       <c r="D125">
         <v>684</v>
@@ -7774,7 +7774,7 @@
         <v>2012</v>
       </c>
       <c r="J125">
-        <v>16.835878613654</v>
+        <v>16.2030812262333</v>
       </c>
       <c r="K125">
         <v>684</v>
@@ -7790,7 +7790,7 @@
         <v>2016</v>
       </c>
       <c r="C126">
-        <v>24.9869441499515</v>
+        <v>24.3346871193122</v>
       </c>
       <c r="D126">
         <v>338</v>
@@ -7804,7 +7804,7 @@
         <v>2012</v>
       </c>
       <c r="J126">
-        <v>24.1334668915574</v>
+        <v>23.2263805939645</v>
       </c>
       <c r="K126">
         <v>382</v>
@@ -7820,7 +7820,7 @@
         <v>2017</v>
       </c>
       <c r="C127">
-        <v>20.2562805920086</v>
+        <v>19.7990298158934</v>
       </c>
       <c r="D127">
         <v>424</v>
@@ -7834,7 +7834,7 @@
         <v>2012</v>
       </c>
       <c r="J127">
-        <v>24.3553836751175</v>
+        <v>23.4399563598633</v>
       </c>
       <c r="K127">
         <v>149</v>
@@ -7850,7 +7850,7 @@
         <v>2017</v>
       </c>
       <c r="C128">
-        <v>23.3052673281612</v>
+        <v>22.7791909083085</v>
       </c>
       <c r="D128">
         <v>377</v>
@@ -7864,7 +7864,7 @@
         <v>2013</v>
       </c>
       <c r="J128">
-        <v>12.40095024081</v>
+        <v>11.97041911188</v>
       </c>
       <c r="K128">
         <v>252</v>
@@ -7880,7 +7880,7 @@
         <v>2017</v>
       </c>
       <c r="C129">
-        <v>33.6775994704493</v>
+        <v>32.9173854506239</v>
       </c>
       <c r="D129">
         <v>788</v>
@@ -7894,7 +7894,7 @@
         <v>2013</v>
       </c>
       <c r="J129">
-        <v>18.1282834644206</v>
+        <v>17.4989131182825</v>
       </c>
       <c r="K129">
         <v>637</v>
@@ -7910,7 +7910,7 @@
         <v>2017</v>
       </c>
       <c r="C130">
-        <v>12.8186792219608</v>
+        <v>12.5293195344115</v>
       </c>
       <c r="D130">
         <v>164</v>
@@ -7924,7 +7924,7 @@
         <v>2013</v>
       </c>
       <c r="J130">
-        <v>24.4241652154086</v>
+        <v>23.5762170163457</v>
       </c>
       <c r="K130">
         <v>385</v>
@@ -7940,7 +7940,7 @@
         <v>2017</v>
       </c>
       <c r="C131">
-        <v>19.5850738617502</v>
+        <v>19.1429744258304</v>
       </c>
       <c r="D131">
         <v>726</v>
@@ -7954,7 +7954,7 @@
         <v>2013</v>
       </c>
       <c r="J131">
-        <v>18.56392870033</v>
+        <v>17.919433800703</v>
       </c>
       <c r="K131">
         <v>928</v>
@@ -7970,7 +7970,7 @@
         <v>2018</v>
       </c>
       <c r="C132">
-        <v>19.8733406537143</v>
+        <v>19.5062342264151</v>
       </c>
       <c r="D132">
         <v>647</v>
@@ -7984,7 +7984,7 @@
         <v>2013</v>
       </c>
       <c r="J132">
-        <v>32.5111281383805</v>
+        <v>31.3824200613056</v>
       </c>
       <c r="K132">
         <v>1134</v>
@@ -8000,7 +8000,7 @@
         <v>2018</v>
       </c>
       <c r="C133">
-        <v>23.6240387376296</v>
+        <v>23.1876482680822</v>
       </c>
       <c r="D133">
         <v>333</v>
@@ -8014,7 +8014,7 @@
         <v>2013</v>
       </c>
       <c r="J133">
-        <v>20.8723644192456</v>
+        <v>20.1477261905328</v>
       </c>
       <c r="K133">
         <v>159</v>
@@ -8030,7 +8030,7 @@
         <v>2018</v>
       </c>
       <c r="C134">
-        <v>34.7262712378904</v>
+        <v>34.0847969337108</v>
       </c>
       <c r="D134">
         <v>760</v>
@@ -8044,7 +8044,7 @@
         <v>2014</v>
       </c>
       <c r="J134">
-        <v>19.5821728773559</v>
+        <v>18.9478971776083</v>
       </c>
       <c r="K134">
         <v>982</v>
@@ -8060,7 +8060,7 @@
         <v>2018</v>
       </c>
       <c r="C135">
-        <v>12.6933757789217</v>
+        <v>12.4588998589563</v>
       </c>
       <c r="D135">
         <v>156</v>
@@ -8074,7 +8074,7 @@
         <v>2014</v>
       </c>
       <c r="J135">
-        <v>25.2030637629731</v>
+        <v>24.3867247895526</v>
       </c>
       <c r="K135">
         <v>369</v>
@@ -8090,7 +8090,7 @@
         <v>2018</v>
       </c>
       <c r="C136">
-        <v>18.9084936331617</v>
+        <v>18.5592101551481</v>
       </c>
       <c r="D136">
         <v>429</v>
@@ -8104,7 +8104,7 @@
         <v>2014</v>
       </c>
       <c r="J136">
-        <v>18.5907590145828</v>
+        <v>17.9885956715939</v>
       </c>
       <c r="K136">
         <v>584</v>
@@ -8120,7 +8120,7 @@
         <v>2019</v>
       </c>
       <c r="C137">
-        <v>19.9458354137374</v>
+        <v>19.6418756120482</v>
       </c>
       <c r="D137">
         <v>412</v>
@@ -8134,7 +8134,7 @@
         <v>2014</v>
       </c>
       <c r="J137">
-        <v>33.6251192117581</v>
+        <v>32.5359859398423</v>
       </c>
       <c r="K137">
         <v>1040</v>
@@ -8150,7 +8150,7 @@
         <v>2019</v>
       </c>
       <c r="C138">
-        <v>23.7858075293662</v>
+        <v>23.4233293884574</v>
       </c>
       <c r="D138">
         <v>336</v>
@@ -8164,7 +8164,7 @@
         <v>2014</v>
       </c>
       <c r="J138">
-        <v>23.2688710769772</v>
+        <v>22.5151815054918</v>
       </c>
       <c r="K138">
         <v>158</v>
@@ -8180,7 +8180,7 @@
         <v>2019</v>
       </c>
       <c r="C139">
-        <v>35.2284201819444</v>
+        <v>34.6915650745893</v>
       </c>
       <c r="D139">
         <v>748</v>
@@ -8194,7 +8194,7 @@
         <v>2014</v>
       </c>
       <c r="J139">
-        <v>12.3056656374203</v>
+        <v>11.9070793961528</v>
       </c>
       <c r="K139">
         <v>224</v>
@@ -8210,7 +8210,7 @@
         <v>2019</v>
       </c>
       <c r="C140">
-        <v>12.8375077463326</v>
+        <v>12.6418736087886</v>
       </c>
       <c r="D140">
         <v>138</v>
@@ -8224,7 +8224,7 @@
         <v>2015</v>
       </c>
       <c r="J140">
-        <v>11.9243468274476</v>
+        <v>11.5665583456425</v>
       </c>
       <c r="K140">
         <v>190</v>
@@ -8240,7 +8240,7 @@
         <v>2019</v>
       </c>
       <c r="C141">
-        <v>20.7349656324808</v>
+        <v>20.4189800690312</v>
       </c>
       <c r="D141">
         <v>620</v>
@@ -8254,7 +8254,7 @@
         <v>2015</v>
       </c>
       <c r="J141">
-        <v>18.3910343532688</v>
+        <v>17.8392137499856</v>
       </c>
       <c r="K141">
         <v>484</v>
@@ -8270,7 +8270,7 @@
         <v>2020</v>
       </c>
       <c r="C142">
-        <v>21.008285111239</v>
+        <v>20.7471228942451</v>
       </c>
       <c r="D142">
         <v>544</v>
@@ -8284,7 +8284,7 @@
         <v>2015</v>
       </c>
       <c r="J142">
-        <v>32.8610284281229</v>
+        <v>31.8750375271548</v>
       </c>
       <c r="K142">
         <v>919</v>
@@ -8300,7 +8300,7 @@
         <v>2020</v>
       </c>
       <c r="C143">
-        <v>33.8125851550022</v>
+        <v>33.3922476712611</v>
       </c>
       <c r="D143">
         <v>710</v>
@@ -8314,7 +8314,7 @@
         <v>2015</v>
       </c>
       <c r="J143">
-        <v>19.5431809914102</v>
+        <v>18.9567903775056</v>
       </c>
       <c r="K143">
         <v>762</v>
@@ -8330,7 +8330,7 @@
         <v>2020</v>
       </c>
       <c r="C144">
-        <v>14.2121585189294</v>
+        <v>14.0354816122986</v>
       </c>
       <c r="D144">
         <v>119</v>
@@ -8344,7 +8344,7 @@
         <v>2015</v>
       </c>
       <c r="J144">
-        <v>25.5836948867916</v>
+        <v>24.8160594359811</v>
       </c>
       <c r="K144">
         <v>254</v>
@@ -8360,7 +8360,7 @@
         <v>2020</v>
       </c>
       <c r="C145">
-        <v>20.9757351199118</v>
+        <v>20.7149775446035</v>
       </c>
       <c r="D145">
         <v>359</v>
@@ -8374,7 +8374,7 @@
         <v>2015</v>
       </c>
       <c r="J145">
-        <v>23.8922478431879</v>
+        <v>23.1753640418003</v>
       </c>
       <c r="K145">
         <v>141</v>
@@ -8390,7 +8390,7 @@
         <v>2020</v>
       </c>
       <c r="C146">
-        <v>26.0530927852422</v>
+        <v>25.7292165890029</v>
       </c>
       <c r="D146">
         <v>280</v>
@@ -8404,7 +8404,7 @@
         <v>2016</v>
       </c>
       <c r="J146">
-        <v>34.4173807540989</v>
+        <v>33.5189524213531</v>
       </c>
       <c r="K146">
         <v>825</v>
@@ -8420,7 +8420,7 @@
         <v>2021</v>
       </c>
       <c r="C147">
-        <v>13.9028056112224</v>
+        <v>13.7774851876234</v>
       </c>
       <c r="D147">
         <v>125</v>
@@ -8434,7 +8434,7 @@
         <v>2016</v>
       </c>
       <c r="J147">
-        <v>19.1165093121345</v>
+        <v>18.6174936051599</v>
       </c>
       <c r="K147">
         <v>514</v>
@@ -8450,7 +8450,7 @@
         <v>2021</v>
       </c>
       <c r="C148">
-        <v>33.8927539890419</v>
+        <v>33.5872434032207</v>
       </c>
       <c r="D148">
         <v>731</v>
@@ -8464,7 +8464,7 @@
         <v>2016</v>
       </c>
       <c r="J148">
-        <v>12.4130385127468</v>
+        <v>12.0890096281842</v>
       </c>
       <c r="K148">
         <v>172</v>
@@ -8480,7 +8480,7 @@
         <v>2021</v>
       </c>
       <c r="C149">
-        <v>20.6401609466645</v>
+        <v>20.4541097433807</v>
       </c>
       <c r="D149">
         <v>570</v>
@@ -8494,7 +8494,7 @@
         <v>2016</v>
       </c>
       <c r="J149">
-        <v>20.2508929851644</v>
+        <v>19.7222654248261</v>
       </c>
       <c r="K149">
         <v>684</v>
@@ -8510,7 +8510,7 @@
         <v>2021</v>
       </c>
       <c r="C150">
-        <v>21.9094314723311</v>
+        <v>21.7119390157934</v>
       </c>
       <c r="D150">
         <v>325</v>
@@ -8524,7 +8524,7 @@
         <v>2016</v>
       </c>
       <c r="J150">
-        <v>25.8087585194041</v>
+        <v>25.1350489174883</v>
       </c>
       <c r="K150">
         <v>210</v>
@@ -8540,7 +8540,7 @@
         <v>2021</v>
       </c>
       <c r="C151">
-        <v>25.6336919840925</v>
+        <v>25.4026289003032</v>
       </c>
       <c r="D151">
         <v>278</v>
@@ -8554,7 +8554,7 @@
         <v>2016</v>
       </c>
       <c r="J151">
-        <v>23.3105710898938</v>
+        <v>22.7020739567367</v>
       </c>
       <c r="K151">
         <v>128</v>
@@ -8570,7 +8570,7 @@
         <v>2022</v>
       </c>
       <c r="C152">
-        <v>33.2296157253438</v>
+        <v>33.0489421786656</v>
       </c>
       <c r="D152">
         <v>752</v>
@@ -8584,7 +8584,7 @@
         <v>2017</v>
       </c>
       <c r="J152">
-        <v>20.2562805920086</v>
+        <v>19.7990298158934</v>
       </c>
       <c r="K152">
         <v>424</v>
@@ -8600,7 +8600,7 @@
         <v>2022</v>
       </c>
       <c r="C153">
-        <v>20.2833489542903</v>
+        <v>20.1730658675289</v>
       </c>
       <c r="D153">
         <v>521</v>
@@ -8614,7 +8614,7 @@
         <v>2017</v>
       </c>
       <c r="J153">
-        <v>23.7283936573868</v>
+        <v>23.1927658867047</v>
       </c>
       <c r="K153">
         <v>225</v>
@@ -8630,7 +8630,7 @@
         <v>2022</v>
       </c>
       <c r="C154">
-        <v>20.0644610903354</v>
+        <v>19.9553681240688</v>
       </c>
       <c r="D154">
         <v>290</v>
@@ -8644,7 +8644,7 @@
         <v>2017</v>
       </c>
       <c r="J154">
-        <v>33.6775994704493</v>
+        <v>32.9173854506239</v>
       </c>
       <c r="K154">
         <v>788</v>
@@ -8660,7 +8660,7 @@
         <v>2022</v>
       </c>
       <c r="C155">
-        <v>24.4879906655463</v>
+        <v>24.3548464197285</v>
       </c>
       <c r="D155">
         <v>252</v>
@@ -8674,7 +8674,7 @@
         <v>2017</v>
       </c>
       <c r="J155">
-        <v>22.8667291773051</v>
+        <v>22.3505520037095</v>
       </c>
       <c r="K155">
         <v>152</v>
@@ -8690,7 +8690,7 @@
         <v>2022</v>
       </c>
       <c r="C156">
-        <v>14.5428254413715</v>
+        <v>14.4637542937262</v>
       </c>
       <c r="D156">
         <v>110</v>
@@ -8704,7 +8704,7 @@
         <v>2017</v>
       </c>
       <c r="J156">
-        <v>12.8186792219608</v>
+        <v>12.5293195344115</v>
       </c>
       <c r="K156">
         <v>164</v>
@@ -8713,17 +8713,17 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="B157">
         <v>2023</v>
       </c>
       <c r="C157">
-        <v>20.5793456173728</v>
+        <v>33.893466252585</v>
       </c>
       <c r="D157">
-        <v>519</v>
+        <v>754</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>2017</v>
       </c>
       <c r="J157">
-        <v>19.5850738617502</v>
+        <v>19.1429744258304</v>
       </c>
       <c r="K157">
         <v>726</v>
@@ -8743,17 +8743,17 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Associate degree-all</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="B158">
         <v>2023</v>
       </c>
       <c r="C158">
-        <v>25.5183064897793</v>
+        <v>20.5335481883329</v>
       </c>
       <c r="D158">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>2018</v>
       </c>
       <c r="J158">
-        <v>19.8733406537143</v>
+        <v>19.5062342264151</v>
       </c>
       <c r="K158">
         <v>647</v>
@@ -8773,17 +8773,17 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>Associate degree-all</t>
         </is>
       </c>
       <c r="B159">
         <v>2023</v>
       </c>
       <c r="C159">
-        <v>20.603536008966</v>
+        <v>25.4316237642176</v>
       </c>
       <c r="D159">
-        <v>317</v>
+        <v>266</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>2018</v>
       </c>
       <c r="J159">
-        <v>22.9225075958674</v>
+        <v>22.499076024151</v>
       </c>
       <c r="K159">
         <v>136</v>
@@ -8803,17 +8803,17 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="B160">
         <v>2023</v>
       </c>
       <c r="C160">
-        <v>15.4406855107946</v>
+        <v>20.5094399686926</v>
       </c>
       <c r="D160">
-        <v>121</v>
+        <v>519</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>2018</v>
       </c>
       <c r="J160">
-        <v>34.7262712378904</v>
+        <v>34.0847969337108</v>
       </c>
       <c r="K160">
         <v>760</v>
@@ -8833,17 +8833,17 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="B161">
         <v>2023</v>
       </c>
       <c r="C161">
-        <v>34.0089908475046</v>
+        <v>15.3882352941176</v>
       </c>
       <c r="D161">
-        <v>754</v>
+        <v>121</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>2018</v>
       </c>
       <c r="J161">
-        <v>12.6933757789217</v>
+        <v>12.4588998589563</v>
       </c>
       <c r="K161">
         <v>156</v>
@@ -8884,7 +8884,7 @@
         <v>2018</v>
       </c>
       <c r="J162">
-        <v>18.9084936331617</v>
+        <v>18.5592101551481</v>
       </c>
       <c r="K162">
         <v>429</v>
@@ -8893,17 +8893,17 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Associate degree-all</t>
         </is>
       </c>
       <c r="B163">
         <v>2024</v>
       </c>
       <c r="C163">
-        <v>21.4175555419922</v>
+        <v>26.3682276916504</v>
       </c>
       <c r="D163">
-        <v>504</v>
+        <v>285</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>2018</v>
       </c>
       <c r="J163">
-        <v>24.1391669505659</v>
+        <v>23.6932608751047</v>
       </c>
       <c r="K163">
         <v>197</v>
@@ -8923,17 +8923,17 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Associate degree-all</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="B164">
         <v>2024</v>
       </c>
       <c r="C164">
-        <v>26.3682276916504</v>
+        <v>20.2551110839844</v>
       </c>
       <c r="D164">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>2019</v>
       </c>
       <c r="J164">
-        <v>19.9458354137374</v>
+        <v>19.6418756120482</v>
       </c>
       <c r="K164">
         <v>412</v>
@@ -8953,17 +8953,17 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="B165">
         <v>2024</v>
       </c>
       <c r="C165">
-        <v>20.2551110839844</v>
+        <v>21.4175555419922</v>
       </c>
       <c r="D165">
-        <v>332</v>
+        <v>504</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>2019</v>
       </c>
       <c r="J165">
-        <v>23.7656241163667</v>
+        <v>23.4034535557665</v>
       </c>
       <c r="K165">
         <v>141</v>
@@ -9004,7 +9004,7 @@
         <v>2019</v>
       </c>
       <c r="J166">
-        <v>35.2284201819444</v>
+        <v>34.6915650745893</v>
       </c>
       <c r="K166">
         <v>748</v>
@@ -9020,7 +9020,7 @@
         <v>2019</v>
       </c>
       <c r="J167">
-        <v>12.8375077463326</v>
+        <v>12.6418736087886</v>
       </c>
       <c r="K167">
         <v>138</v>
@@ -9036,7 +9036,7 @@
         <v>2019</v>
       </c>
       <c r="J168">
-        <v>20.7349656324808</v>
+        <v>20.4189800690312</v>
       </c>
       <c r="K168">
         <v>620</v>
@@ -9052,7 +9052,7 @@
         <v>2019</v>
       </c>
       <c r="J169">
-        <v>23.8156729825574</v>
+        <v>23.4527397141977</v>
       </c>
       <c r="K169">
         <v>195</v>
@@ -9068,7 +9068,7 @@
         <v>2020</v>
       </c>
       <c r="J170">
-        <v>21.008285111239</v>
+        <v>20.7471228942451</v>
       </c>
       <c r="K170">
         <v>544</v>
@@ -9084,7 +9084,7 @@
         <v>2020</v>
       </c>
       <c r="J171">
-        <v>33.8125851550022</v>
+        <v>33.3922476712611</v>
       </c>
       <c r="K171">
         <v>710</v>
@@ -9100,7 +9100,7 @@
         <v>2020</v>
       </c>
       <c r="J172">
-        <v>14.2121585189294</v>
+        <v>14.0354816122986</v>
       </c>
       <c r="K172">
         <v>119</v>
@@ -9116,7 +9116,7 @@
         <v>2020</v>
       </c>
       <c r="J173">
-        <v>20.9757351199118</v>
+        <v>20.7149775446035</v>
       </c>
       <c r="K173">
         <v>359</v>
@@ -9132,7 +9132,7 @@
         <v>2020</v>
       </c>
       <c r="J174">
-        <v>25.6915467176117</v>
+        <v>25.3721650420849</v>
       </c>
       <c r="K174">
         <v>162</v>
@@ -9148,7 +9148,7 @@
         <v>2020</v>
       </c>
       <c r="J175">
-        <v>26.3933256018062</v>
+        <v>26.0652198382224</v>
       </c>
       <c r="K175">
         <v>118</v>
@@ -9164,7 +9164,7 @@
         <v>2021</v>
       </c>
       <c r="J176">
-        <v>13.9028056112224</v>
+        <v>13.7774851876234</v>
       </c>
       <c r="K176">
         <v>125</v>
@@ -9180,7 +9180,7 @@
         <v>2021</v>
       </c>
       <c r="J177">
-        <v>33.8927539890419</v>
+        <v>33.5872434032207</v>
       </c>
       <c r="K177">
         <v>731</v>
@@ -9196,7 +9196,7 @@
         <v>2021</v>
       </c>
       <c r="J178">
-        <v>20.6401609466645</v>
+        <v>20.4541097433807</v>
       </c>
       <c r="K178">
         <v>570</v>
@@ -9212,7 +9212,7 @@
         <v>2021</v>
       </c>
       <c r="J179">
-        <v>21.9094314723311</v>
+        <v>21.7119390157934</v>
       </c>
       <c r="K179">
         <v>325</v>
@@ -9228,7 +9228,7 @@
         <v>2021</v>
       </c>
       <c r="J180">
-        <v>24.2817132076424</v>
+        <v>24.0628369124552</v>
       </c>
       <c r="K180">
         <v>169</v>
@@ -9244,7 +9244,7 @@
         <v>2021</v>
       </c>
       <c r="J181">
-        <v>26.9401214786904</v>
+        <v>26.6972821892744</v>
       </c>
       <c r="K181">
         <v>109</v>
@@ -9260,7 +9260,7 @@
         <v>2022</v>
       </c>
       <c r="J182">
-        <v>33.2296157253438</v>
+        <v>33.0489421786656</v>
       </c>
       <c r="K182">
         <v>752</v>
@@ -9276,7 +9276,7 @@
         <v>2022</v>
       </c>
       <c r="J183">
-        <v>20.2833489542903</v>
+        <v>20.1730658675289</v>
       </c>
       <c r="K183">
         <v>521</v>
@@ -9292,7 +9292,7 @@
         <v>2022</v>
       </c>
       <c r="J184">
-        <v>20.0644610903354</v>
+        <v>19.9553681240688</v>
       </c>
       <c r="K184">
         <v>290</v>
@@ -9308,7 +9308,7 @@
         <v>2022</v>
       </c>
       <c r="J185">
-        <v>25.053705069585</v>
+        <v>24.9174849643101</v>
       </c>
       <c r="K185">
         <v>97</v>
@@ -9324,7 +9324,7 @@
         <v>2022</v>
       </c>
       <c r="J186">
-        <v>24.0457126467142</v>
+        <v>23.9149731214006</v>
       </c>
       <c r="K186">
         <v>155</v>
@@ -9340,7 +9340,7 @@
         <v>2022</v>
       </c>
       <c r="J187">
-        <v>14.5428254413715</v>
+        <v>14.4637542937262</v>
       </c>
       <c r="K187">
         <v>110</v>
@@ -9349,81 +9349,81 @@
     <row r="188">
       <c r="H188" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Bachelor's degree or more</t>
         </is>
       </c>
       <c r="I188">
         <v>2023</v>
       </c>
       <c r="J188">
-        <v>20.5793456173728</v>
+        <v>33.893466252585</v>
       </c>
       <c r="K188">
-        <v>519</v>
+        <v>754</v>
       </c>
     </row>
     <row r="189">
       <c r="H189" t="inlineStr">
         <is>
-          <t>Associate degree-occupational/vocational</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="I189">
         <v>2023</v>
       </c>
       <c r="J189">
-        <v>25.9550592943366</v>
+        <v>20.5335481883329</v>
       </c>
       <c r="K189">
-        <v>140</v>
+        <v>317</v>
       </c>
     </row>
     <row r="190">
       <c r="H190" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>Associate degree-occupational/vocational</t>
         </is>
       </c>
       <c r="I190">
         <v>2023</v>
       </c>
       <c r="J190">
-        <v>20.603536008966</v>
+        <v>25.8668929701861</v>
       </c>
       <c r="K190">
-        <v>317</v>
+        <v>140</v>
       </c>
     </row>
     <row r="191">
       <c r="H191" t="inlineStr">
         <is>
-          <t>No HS diploma</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="I191">
         <v>2023</v>
       </c>
       <c r="J191">
-        <v>15.4406855107946</v>
+        <v>20.5094399686926</v>
       </c>
       <c r="K191">
-        <v>121</v>
+        <v>519</v>
       </c>
     </row>
     <row r="192">
       <c r="H192" t="inlineStr">
         <is>
-          <t>Bachelor's degree or more</t>
+          <t>No HS diploma</t>
         </is>
       </c>
       <c r="I192">
         <v>2023</v>
       </c>
       <c r="J192">
-        <v>34.0089908475046</v>
+        <v>15.3882352941176</v>
       </c>
       <c r="K192">
-        <v>754</v>
+        <v>121</v>
       </c>
     </row>
     <row r="193">
@@ -9436,7 +9436,7 @@
         <v>2023</v>
       </c>
       <c r="J193">
-        <v>25.0773206278234</v>
+        <v>24.9921358800552</v>
       </c>
       <c r="K193">
         <v>126</v>
@@ -9461,49 +9461,49 @@
     <row r="195">
       <c r="H195" t="inlineStr">
         <is>
-          <t>HS graduate</t>
+          <t>Associate degree-occupational/vocational</t>
         </is>
       </c>
       <c r="I195">
         <v>2024</v>
       </c>
       <c r="J195">
-        <v>21.4175555419922</v>
+        <v>26.2357777404785</v>
       </c>
       <c r="K195">
-        <v>504</v>
+        <v>166</v>
       </c>
     </row>
     <row r="196">
       <c r="H196" t="inlineStr">
         <is>
-          <t>Associate degree-occupational/vocational</t>
+          <t>Some college but no degree</t>
         </is>
       </c>
       <c r="I196">
         <v>2024</v>
       </c>
       <c r="J196">
-        <v>26.2357777404785</v>
+        <v>20.2551110839844</v>
       </c>
       <c r="K196">
-        <v>166</v>
+        <v>332</v>
       </c>
     </row>
     <row r="197">
       <c r="H197" t="inlineStr">
         <is>
-          <t>Some college but no degree</t>
+          <t>HS graduate</t>
         </is>
       </c>
       <c r="I197">
         <v>2024</v>
       </c>
       <c r="J197">
-        <v>20.2551110839844</v>
+        <v>21.4175555419922</v>
       </c>
       <c r="K197">
-        <v>332</v>
+        <v>504</v>
       </c>
     </row>
     <row r="198">
